--- a/results/scraped_Cape_Town_Performing_Arts_and_Music_Groups.xlsx
+++ b/results/scraped_Cape_Town_Performing_Arts_and_Music_Groups.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="389">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -184,6 +184,60 @@
     <t>Cinemas inHyderabad- Cinema Halls and MovieTheatreNear You in ...</t>
   </si>
   <si>
+    <t>Ilovepdfと言うサイトを発見しました。 - https://www... - Yahoo!知恵袋</t>
+  </si>
+  <si>
+    <t>Free Sewing Patterns - Reddit</t>
+  </si>
+  <si>
+    <t>至急!PCでの‘’lLovePDF"の解約についてです。この... - Yahoo!知恵袋</t>
+  </si>
+  <si>
+    <t>I love pdf : r/pdf - Reddit</t>
+  </si>
+  <si>
+    <t>I LOVE PDF在线转换，安全吗？ - 知乎</t>
+  </si>
+  <si>
+    <t>i love pdf 是突然收费了吗？昨天打开200M+的文件还无压力，今天就 …</t>
+  </si>
+  <si>
+    <t>This is super random but I want to share iLovePDF.com with everyone ...</t>
+  </si>
+  <si>
+    <t>Advanced Placement European History - Reddit</t>
+  </si>
+  <si>
+    <t>COMPLETED! Arthur's Journal PDF and ZIP - Reddit</t>
+  </si>
+  <si>
+    <t>Hundreds of Kalimba Tabs and Sheet Music (translated/organized)</t>
+  </si>
+  <si>
+    <t>YouTube Music</t>
+  </si>
+  <si>
+    <t>TheMusicChannel -YouTube</t>
+  </si>
+  <si>
+    <t>Spotify - Web Player:Musicfor everyone</t>
+  </si>
+  <si>
+    <t>YouTubeMusic</t>
+  </si>
+  <si>
+    <t>Home - JioSaavn - Listen to New &amp; Old Indian &amp; English Songs.</t>
+  </si>
+  <si>
+    <t>‎AppleMusic- Web Player</t>
+  </si>
+  <si>
+    <t>AmazonMusic| Listen to songs, podcasts, &amp; more</t>
+  </si>
+  <si>
+    <t>Download Latest MP3 Songs Online: Play Old &amp; New MP3Music…</t>
+  </si>
+  <si>
     <t>[found sos] cant login whatsapp browser - Lowyat.NET</t>
   </si>
   <si>
@@ -211,51 +265,6 @@
     <t>FB, IG &amp; Whatsapp Subscriptions Are Here! - Lowyat.NET</t>
   </si>
   <si>
-    <t>YouTube Music</t>
-  </si>
-  <si>
-    <t>Spotify - Web Player:Musicfor everyone</t>
-  </si>
-  <si>
-    <t>TheMusicChannel -YouTube</t>
-  </si>
-  <si>
-    <t>YouTubeMusic- YouTube</t>
-  </si>
-  <si>
-    <t>Home - JioSaavn - Listen to New &amp; Old Indian &amp; English Songs.</t>
-  </si>
-  <si>
-    <t>‎AppleMusic- Web Player</t>
-  </si>
-  <si>
-    <t>Spotify – Web Player</t>
-  </si>
-  <si>
-    <t>Download Latest MP3 Songs Online: Play Old &amp; New MP3Music…</t>
-  </si>
-  <si>
-    <t>UDISE+</t>
-  </si>
-  <si>
-    <t>SDMS - UDISEPLUS</t>
-  </si>
-  <si>
-    <t>Sign In -UDISE+</t>
-  </si>
-  <si>
-    <t>UDISE+Teacher</t>
-  </si>
-  <si>
-    <t>UDISE+Student Module - UDISEPLUS</t>
-  </si>
-  <si>
-    <t>UDISE+Account</t>
-  </si>
-  <si>
-    <t>UDISE + Profile</t>
-  </si>
-  <si>
     <t>Community-Wikipedia</t>
   </si>
   <si>
@@ -316,223 +325,277 @@
     <t>MarchingBand Command Fundamentals | PDF | Foot | Sports - Scribd</t>
   </si>
   <si>
-    <t>现在怎么才能登录WhatsApp呢？ - 知乎</t>
-  </si>
-  <si>
-    <t>whatsapp messenger - 知乎</t>
-  </si>
-  <si>
-    <t>怎样在whatsapp中加好友-百度经验</t>
-  </si>
-  <si>
-    <t>Win10的磁盘管理在哪里 怎么打开磁盘管理工具-百度经验</t>
-  </si>
-  <si>
-    <t>WhatsApp号码被封号，禁止使用怎么办？ - 知乎</t>
-  </si>
-  <si>
-    <t>WhatsApp 整个软件删除了，一直都是有备份的，这次重新安装却说找 …</t>
-  </si>
-  <si>
-    <t>WhatsApp还有什么有什么优势吗相比较微信和QQ? - 知乎</t>
-  </si>
-  <si>
-    <t>微信与 WhatsApp 谁抄的谁？ - 知乎</t>
-  </si>
-  <si>
-    <t>微信与 WhatsApp 、Messenger 等国外同类通讯 App 比有什么优点与 …</t>
-  </si>
-  <si>
-    <t>WhatsApp如何养号，防止封号？ - 知乎</t>
-  </si>
-  <si>
-    <t>Google Translate</t>
-  </si>
-  <si>
-    <t>iQIYI -Asian Dramas | Watch Free Streaming Online with…</t>
-  </si>
-  <si>
-    <t>Watch Chinese, Korean, Japanese &amp; Thai Dramas with …</t>
-  </si>
-  <si>
-    <t>Drama TVSerials - WatchLatest Drama TV Show Episodes…</t>
-  </si>
-  <si>
-    <t>Error 570 - Adhaar e-KYC authentication API implemetation in PHP</t>
-  </si>
-  <si>
-    <t>how to integrate aadhaar verification API to java(spring mvc) web ...</t>
-  </si>
-  <si>
-    <t>How to use AADHAR authentication api using OTP request</t>
-  </si>
-  <si>
-    <t>java - How To integrate Aadhaar Card Authentication Api for Aadhaar ...</t>
-  </si>
-  <si>
-    <t>How to perform Aadhaar eKYC Authentication via UIDAI and retrieve …</t>
-  </si>
-  <si>
-    <t>How to implement UIDAI Aadhar APIs in asp.net c# and Android?</t>
-  </si>
-  <si>
-    <t>Is there a way to call UIDAI (Aadhaar) API from PHP?</t>
-  </si>
-  <si>
-    <t>How to undo a successful "git cherry-pick"? - Stack Overflow</t>
-  </si>
-  <si>
-    <t>.gitignore syntax - how to exclude virtualenv sub-directories?</t>
-  </si>
-  <si>
-    <t>java - Exception during UIDAI authentication - Stack Overflow</t>
-  </si>
-  <si>
-    <t>ChineseModels - xChina</t>
-  </si>
-  <si>
-    <t>ChineseCartoons 2 - Playlist - hanime.tv</t>
-  </si>
-  <si>
-    <t>ChineseDrama - Sexual Content- CPOP HOME</t>
-  </si>
-  <si>
-    <t>ChinaUncensored</t>
-  </si>
-  <si>
-    <t>Chinese Beautiful, Famous &amp; Sexy ActresseS-IMDb</t>
-  </si>
-  <si>
-    <t>Sexand love inChina-South China Morning Post</t>
-  </si>
-  <si>
-    <t>XXX- Trailers &amp; Videos |Rotten Tomatoes</t>
-  </si>
-  <si>
-    <t>166+ FreeChinese4K &amp; HD Stock Videos - Pixabay</t>
-  </si>
-  <si>
-    <t>Sex and the City - Women'sSexinChina</t>
-  </si>
-  <si>
-    <t>xXx|</t>
-  </si>
-  <si>
-    <t>IRONMAN Triathlon - Races, Training &amp; Stories</t>
-  </si>
-  <si>
-    <t>2026 IRONMAN 70.3 World Championship</t>
-  </si>
-  <si>
-    <t>IRONMAN</t>
-  </si>
-  <si>
-    <t>my.ironman.com</t>
-  </si>
-  <si>
-    <t>IRONMAN - Events</t>
-  </si>
-  <si>
-    <t>2026 IRONMAN 70.3 Italy Emilia-Romagna - Sunday, September 20, …</t>
-  </si>
-  <si>
-    <t>2026 IRONMAN Wales - Sunday, September 13, 2026</t>
-  </si>
-  <si>
-    <t>2026 IRONMAN 70.3 Erkner - Sunday, September 13, 2026</t>
-  </si>
-  <si>
-    <t>IRONMAN Insider™, A Triathlon Podcast Presented by Maurten</t>
-  </si>
-  <si>
-    <t>Races | IRONMAN</t>
-  </si>
-  <si>
-    <t>Skype Account - Microsoft Community</t>
-  </si>
-  <si>
-    <t>Home - JioSaavn - Listen to New &amp; Old Indian &amp; English …</t>
-  </si>
-  <si>
-    <t>Official Website of Sport LisboaeBenfica-SL Benfica</t>
-  </si>
-  <si>
-    <t>S.L. Benfica-Wikipedia</t>
-  </si>
-  <si>
-    <t>Site Oficial do Sport Lisboa eBenfica-SL Benfica</t>
-  </si>
-  <si>
-    <t>SL Benfica - Club profile| Transfermarkt</t>
-  </si>
-  <si>
-    <t>Benficalive score, schedule &amp; player stats | Sofascore</t>
-  </si>
-  <si>
-    <t>SL Benfica- Detailed squad 26/27 | Transfermarkt</t>
-  </si>
-  <si>
-    <t>2025–26S.L. Benficaseason - Wikipedia</t>
-  </si>
-  <si>
-    <t>S.L. Benfica- Wikiwand</t>
-  </si>
-  <si>
-    <t>SL Benfica— O Glorioso | Portal do Adepto</t>
-  </si>
-  <si>
-    <t>Orchestra: vêtements enfants et bébés 0-14 ans, chaussures, …</t>
-  </si>
-  <si>
-    <t>Google Chrome'u indirme ve yükleme</t>
-  </si>
-  <si>
-    <t>A Google Chrome letöltése és telepítése</t>
-  </si>
-  <si>
-    <t>Chrome 다운로드 및 설치 - 컴퓨터 - Google Chrome 고객센터</t>
-  </si>
-  <si>
-    <t>Google Chrome को डाउनलोड और इंस्टॉल करना</t>
-  </si>
-  <si>
-    <t>Télécharger et installer Google Chrome</t>
-  </si>
-  <si>
-    <t>Bantuan Google Chrome</t>
-  </si>
-  <si>
-    <t>Google Chrome Help</t>
-  </si>
-  <si>
-    <t>Download Chrome - Google Help</t>
-  </si>
-  <si>
-    <t>Baixar o Chrome - Ajuda do Google Chrome</t>
-  </si>
-  <si>
-    <t>กำหนดให้ Chrome เป็นเบราว์เซอร์เริ่มต้น</t>
-  </si>
-  <si>
-    <t>YouTube</t>
-  </si>
-  <si>
-    <t>YouTube-YouTube</t>
-  </si>
-  <si>
-    <t>YouTube-Wikipedia</t>
-  </si>
-  <si>
-    <t>YouTube - Apps on Google Play</t>
-  </si>
-  <si>
-    <t>YTIndustries | Mountain Bikes | Live Uncaged</t>
-  </si>
-  <si>
-    <t>YouTubeHelp</t>
-  </si>
-  <si>
-    <t>‎YouTube App - App Store</t>
+    <t>ChatGPT MD - GitHub</t>
+  </si>
+  <si>
+    <t>chatgpt · GitHub Topics · GitHub</t>
+  </si>
+  <si>
+    <t>ChatGPT - 知乎</t>
+  </si>
+  <si>
+    <t>r/ChatGPT's FAQ Thread - Reddit</t>
+  </si>
+  <si>
+    <t>ChatGPT - Reddit</t>
+  </si>
+  <si>
+    <t>ChatGPT最实用的提示（Prompts）写法有哪些？ - 知乎</t>
+  </si>
+  <si>
+    <t>ChatGPT for Legacy iOS - GitHub</t>
+  </si>
+  <si>
+    <t>chatgpt-api · GitHub Topics · GitHub</t>
+  </si>
+  <si>
+    <t>awesome-ChatGPT-repositories - GitHub</t>
+  </si>
+  <si>
+    <t>ChatGPT-Bypass - GitHub</t>
+  </si>
+  <si>
+    <t>File Explorer in Windows|MicrosoftSupport</t>
+  </si>
+  <si>
+    <t>Get Help with File Explorer in Windows: Easy Solutions</t>
+  </si>
+  <si>
+    <t>Get Help With File Explorer in Windows11 &amp; 10 (Ultimate Guide)</t>
+  </si>
+  <si>
+    <t>File Explorer| MicrosoftWindows</t>
+  </si>
+  <si>
+    <t>How to OpenWindows File Explorer:Windows11, 10, 8, 7 -wikiHow</t>
+  </si>
+  <si>
+    <t>Windows11File ExplorerFull Tutorial | Complete Guide to ... - YouTube</t>
+  </si>
+  <si>
+    <t>Get Help With File Explorer in Windows11</t>
+  </si>
+  <si>
+    <t>Get Help With File Explorer in Windows11/10</t>
+  </si>
+  <si>
+    <t>Get Help With File Explorer in Windows11 or 10 [Full Guide]</t>
+  </si>
+  <si>
+    <t>Get Help with File Explorer in Windows| A Complete Guide</t>
+  </si>
+  <si>
+    <t>HyderabadMovie Tickets Online Booking &amp; Showtimes near …</t>
+  </si>
+  <si>
+    <t>Movie Theaters &amp; Cinemas Near You inHyderabad</t>
+  </si>
+  <si>
+    <t>Movie Tickets inHyderabad— Today's Showtimes &amp; Bookings …</t>
+  </si>
+  <si>
+    <t>Cinemas inHyderabad- Cinema Halls and MovieTheatreNear …</t>
+  </si>
+  <si>
+    <t>Your AdSense for YouTube account was deactivated</t>
+  </si>
+  <si>
+    <t>YouTube TV Help - Google Help</t>
+  </si>
+  <si>
+    <t>如何在中国大陆用「合法」的方式观看到youtube上面的「有价值」的 …</t>
+  </si>
+  <si>
+    <t>YouTube公司 - 知乎</t>
+  </si>
+  <si>
+    <t>上傳 YouTube 影片</t>
+  </si>
+  <si>
+    <t>创建 YouTube 频道 - YouTube帮助</t>
+  </si>
+  <si>
+    <t>YouTube ความช่วยเหลือ</t>
+  </si>
+  <si>
+    <t>YouTube Trợ giúp</t>
+  </si>
+  <si>
+    <t>YouTube Premium &amp; YouTube Music Premium supported devices</t>
+  </si>
+  <si>
+    <t>Log in met een YouTube-gebruikersnaam - Google Help</t>
+  </si>
+  <si>
+    <t>bard.google.com</t>
+  </si>
+  <si>
+    <t>‎Gemini - chat to supercharge your ideas</t>
+  </si>
+  <si>
+    <t>$80Flights from Singapore(SIN)to Krabi(KBV) |Skyscanner</t>
+  </si>
+  <si>
+    <t>CheapFlightFaresfrom SingaporeChangi (SIN)to Krabi(KBV ...</t>
+  </si>
+  <si>
+    <t>$100Cheap Flights from Singapore Changi to Krabi</t>
+  </si>
+  <si>
+    <t>Singapore to Krabi Flights, Fares @ ₹ 7395 - MakeMyTrip</t>
+  </si>
+  <si>
+    <t>Flights from Singapore to Krabi- Scoot</t>
+  </si>
+  <si>
+    <t>$84Cheap Flights from Singapore (SIN)to Krabi(KBV) -Expedia</t>
+  </si>
+  <si>
+    <t>CheapFlightFaresfrom Singapore to Krabi| Skyscanner</t>
+  </si>
+  <si>
+    <t>CheapFlights from SingaporeChangi (SIN)to Krabi(KBV)</t>
+  </si>
+  <si>
+    <t>Flights from Singapore to KrabiProvince - Skyscanner</t>
+  </si>
+  <si>
+    <t>Book cheapflights from Singapore to Krabi(SIN – KBV)</t>
+  </si>
+  <si>
+    <t>passport size photograph是护照大小的照片，还是护照上的照片？</t>
+  </si>
+  <si>
+    <t>留学passport size，是一定要护照上面的那张照片吗？是不是其他的也 …</t>
+  </si>
+  <si>
+    <t>在美国办理危地马拉签证需要什么材料？ - 知乎</t>
+  </si>
+  <si>
+    <t>英国学校说的passport photo size 到底是多大尺寸?_百度知道</t>
+  </si>
+  <si>
+    <t>What is the size of Philippine passport photo? - Answers</t>
+  </si>
+  <si>
+    <t>How do you make passport size photo on photoshop cs3?</t>
+  </si>
+  <si>
+    <t>passport-size photo 是什么格式_百度知道</t>
+  </si>
+  <si>
+    <t>百度知道 - 全球领先中文互动问答平台</t>
+  </si>
+  <si>
+    <t>毛主席语录：‘’世界是你们的，也是我们的，……‘’的原文是什么？_百 …</t>
+  </si>
+  <si>
+    <t>Madhur MatkaLive Results, Charts &amp; Guessing Tips 2026</t>
+  </si>
+  <si>
+    <t>SattaMatkaResult Today, Full Chart, Jodi and Panel Chart |Madhur...</t>
+  </si>
+  <si>
+    <t>What IsMadhurDay? - SattaMatka11</t>
+  </si>
+  <si>
+    <t>SattaMatka| Live SattaMatkaResult | SattaMatkaOffice</t>
+  </si>
+  <si>
+    <t>MadhurMorning SattaMatkaChart - Panel &amp; Jodi Record | SattaMatka…</t>
+  </si>
+  <si>
+    <t>MadhurLottery | Result Today, Chart &amp; Updates</t>
+  </si>
+  <si>
+    <t>Madhur Matka| SattaMatka|Madhur MatkaResult | ShivpurMatka</t>
+  </si>
+  <si>
+    <t>MadhurDay SattaMatkaChart - Panel &amp; Jodi Record | SattaMatka…</t>
+  </si>
+  <si>
+    <t>MADHURDAY PANEL CHART |MADHURDAY PANNA CHART | SATTAMATKA</t>
+  </si>
+  <si>
+    <t>!MADHUR MATKA| SATTAMATKA| MANIPURMATKA|MADHUR…</t>
+  </si>
+  <si>
+    <t>How to get help in Windows - Microsoft Support</t>
+  </si>
+  <si>
+    <t>About Get Help | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Windows 11 Forum</t>
+  </si>
+  <si>
+    <t>Enable or Disable Tips and Suggestions Notifications in Windows 11</t>
+  </si>
+  <si>
+    <t>ヘルプについて | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Informationen zu Hilfe | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Como obter ajuda no Windows - Suporte da Microsoft</t>
+  </si>
+  <si>
+    <t>Aide et apprentissage Windows | Microsoft Support</t>
+  </si>
+  <si>
+    <t>關於 [取得說明] | Microsoft Support</t>
+  </si>
+  <si>
+    <t>Ausführen von Problembehandlungen in „Hilfe abrufen“</t>
+  </si>
+  <si>
+    <t>301 Moved Permanently</t>
+  </si>
+  <si>
+    <t>Power BI Pro &amp; Power BI Premium: Flexibility to choose the licensing ...</t>
+  </si>
+  <si>
+    <t>New! Get introduced to DAX with Guided Learning | Microsoft Power …</t>
+  </si>
+  <si>
+    <t>An introduction to the Power BI Admin Center</t>
+  </si>
+  <si>
+    <t>Your data. Your visualizations. Your way – with Power BI</t>
+  </si>
+  <si>
+    <t>Public Preview of Multi-Geo for Power BI Premium</t>
+  </si>
+  <si>
+    <t>Unlock retail intelligence with the Power BI app Barcode scanner</t>
+  </si>
+  <si>
+    <t>Power BI May 2022 Feature Summary</t>
+  </si>
+  <si>
+    <t>Visual Awesomeness Unlocked – The Force-Directed Graph</t>
+  </si>
+  <si>
+    <t>Analyzing Black Friday and Cyber Monday Results with Power BI</t>
+  </si>
+  <si>
+    <t>Spider-Man Red Wallpapers- Top FreeSpider-Man Red...</t>
+  </si>
+  <si>
+    <t>Red Spider-Man Wallpapers- Top FreeRed Spider-Man...</t>
+  </si>
+  <si>
+    <t>Spider-Man Wallpaper4K,Redaesthetic, Marvel Superheroes</t>
+  </si>
+  <si>
+    <t>DownloadSpider Man Red Background4kWallpaper|Wallpapers.com</t>
+  </si>
+  <si>
+    <t>[20+]Red Spider-Man Wallpapers| WallpaperSafari</t>
+  </si>
+  <si>
+    <t>Red Spider Man Wallpaper- Pinterest</t>
   </si>
   <si>
     <t>Performing Arts &amp; Music Groups</t>
@@ -541,499 +604,562 @@
     <t>Cape Town</t>
   </si>
   <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e80821a25e14cb6a93faef9f656e53a40f47116fe120369fe55043d31bf9d660JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2hvaXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1a0114fa3b2febceea745bbeb70c3fb8d27a89d7cd6f6009cda64488a3e6d1d6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L2Nob2lyLW11c2lj&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d1ac08901af16d5febbc0023f880c6b18fbb2b43039893952bd55551d2f8c21JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly9sYWdnZWQuY29tL2VuL2cvY2hvaXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=27361746013afa9dfe7933bc002c90dc0cf9e341bbdec62818a05d4aa4410b59JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Nob2ly&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a043aab500095f006c7a48d2d3c0a3265951fd337b6aff7ae4221a673c883aecJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly93d3cuY2hvaXJzY3JpcHQubmV0L2Jsb2cvd2hhdC1pcy1hLWNob2ly&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fda95053fbb3a1c6118bd03446ef6074449ba6500ded93ee811b568a3918a03cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Nob2ly&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a3050181ac528a1a545d298051ae8887181c75bed70b8756a02af870d560104eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0Nob2lyXyhtdXNpYyk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=39c9e9aabac2fa785f4fa98df9ebf5e200bf8779bc338db29edde8cd7f361579JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj0zQ25Ld2RtLS1JTQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9c82fdbbb3a15cfb88d9cf6c18affecf0bd4e7aed5b9478ac7eb16ecf769782dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2Nob2ly&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ef0545822fc109a2790d2480b2c6a41274306c39cb5663e5e9aabafc474ee05fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=28941a5e-de50-6b09-1ee2-0db2df6e6acc&amp;u=a1aHR0cHM6Ly93d3cucm9ja2V0Z2FtZXMuaW8vZ2FtZS9jaG9pcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d842a9bfeec344837ede6765298bd873e3f5183ef6f63b242cc54af1ee2d6e37JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c0fc8dd-8612-6d79-2fa0-df3187946cc2&amp;u=a1aHR0cHM6Ly93d3cuYmFuZC51cy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed5a36c559c32a280b1c29471462088d1b3cb731806c582efcac9eb77595d233JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c0fc8dd-8612-6d79-2fa0-df3187946cc2&amp;u=a1aHR0cHM6Ly93d3cuYmFuZGxhYi5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebd33e0fedbc7c087f0b27a029e2b965fbccea274c2696390d4ac81746f41bfeJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c0fc8dd-8612-6d79-2fa0-df3187946cc2&amp;u=a1aHR0cHM6Ly9wbGF5Lmdvb2dsZS5jb20vc3RvcmUvYXBwcy9kZXRhaWxzP2lkPWNvbS5uaG4uYW5kcm9pZC5iYW5kJmhsPWVuLUlO&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=db568f30bf5ce6c669dde5448baf0f85a4a75f72ee6f766e7a93329cc4066dcdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c0fc8dd-8612-6d79-2fa0-df3187946cc2&amp;u=a1aHR0cHM6Ly9hYm91dC5iYW5kLnVzL2ZlYXR1cmVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=afca3765fe7c166670075cdb171d57ece34d60bb3717e1f5e8bcf42b41efe9e0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c0fc8dd-8612-6d79-2fa0-df3187946cc2&amp;u=a1aHR0cHM6Ly93d3cuYmFuZGxhYi5jb20vc2lnbi11cA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4be74d3ccb0e158c77ee8dfdb98c3b349004769c911dee851627a5e1140789f9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c0fc8dd-8612-6d79-2fa0-df3187946cc2&amp;u=a1aHR0cHM6Ly9hYm91dC5iYW5kLnVzL3Jlc291cmNlcy90dXRvcmlhbHM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c24c9d0b8285020bd3e604866d3897d48efe950fae96ae01126f17c43e334a61JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c0fc8dd-8612-6d79-2fa0-df3187946cc2&amp;u=a1aHR0cHM6Ly9hcGtwdXJlLmNvbS9iYW5kLWFwcC1mb3ItYWxsLWdyb3Vwcy1hcHAvY29tLm5obi5hbmRyb2lkLmJhbmQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6f3f556ff23ca24c2e810c257f4cfa864c44c236b51a706fd56650c999fbc955JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c0fc8dd-8612-6d79-2fa0-df3187946cc2&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQmFuZF8oc29mdHdhcmUp&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=72f12d7c03480241f00c74826bb09a7de681297d7f56463929dafcb1a3f3e6dfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1c0fc8dd-8612-6d79-2fa0-df3187946cc2&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vQGJhbmRhcHA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=80d7134e61016f25655d48dfe883f2ccdb42e213931fa065daa3bfe4fc0c3a89JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT3JjaGVzdHJh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0cfc952d3f2370a72f4a0d258ce022002c2a1ba277c9d98ec79a5b57b37c83b5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L29yY2hlc3RyYS1tdXNpYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c38cb0b65686b08bbf40bdcdadae58d203aa8785629b0a4d76f330367634e8acJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly9hbGxldmVudHMuaW4vYmFuZ2Fsb3JlL29yY2hlc3RyYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d85119416b5e66f69fc231a0730fab224a3d327eacb5b4ac98a11ca1f6a421deJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL09yY2hlc3RyYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c379ef4a83e4842fda05cedfb7fe1d7f370d1473bc7380ca159d18d04cd5407aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly9wcm9tdXNpY2lhbmh1Yi5jb20vd2hhdC1pcy1vcmNoZXN0cmEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66dcbd2626645db7c634ab115d7764daa6f96b4636eb67483dd6b4aa9679ee1cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly9mci5zaG9wLW9yY2hlc3RyYS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16d27f402d10a25ef6882b07346c381a1390f35b011851dbaf17027faacd355dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj04dG1HSjUyUEJjVQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98334e67e166ce9fd39406a24e626f55c238d9197efdd1fb1e8732446733af3bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly93d3cud2lraXdhbmQuY29tL2VuL09yY2hlc3RyYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9cc36a489ee0954c06d8c30f9e79cda4bf9aa99256220e87f8bcdf4df5ca22deJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vcGxheWxpc3Q_bGlzdD1QTEU5REVGODk4QkNDNUE0NzY&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=caa6260cb9ce74759253bb8890070af8fe986d64d6c88c6d0d580a9aec3a5510JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1ad53f39-7f8b-6da2-260d-28d57eb56c75&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29yY2hlc3RyYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f304d6a986bba08d328f016da6c56f491bfe3e684c7c27074c6ac2a4266ce156JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f8a12c3-f331-6d55-1127-052ff2ee6c56&amp;u=a1aHR0cHM6Ly93d3cuaXEuY29tL2RyYW1hP2xhbmc9ZW5fdXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3a46880379a951d37d9ab85ed53d811bd85a963a1dc36160f8b5e7e1a0817583JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f8a12c3-f331-6d55-1127-052ff2ee6c56&amp;u=a1aHR0cHM6Ly93d3cudmlraS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81e1f5f88fb9279f0dbd2874756885494966ccf3aa0088f568aa162f0a097ddaJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f8a12c3-f331-6d55-1127-052ff2ee6c56&amp;u=a1aHR0cHM6Ly93ZXR2LnZpcC9lbi9leHBsb3Jhcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94d43d0397146c199745bb73f141961b228fef1ee0fc7a8262db9f6f3eab0c19JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f8a12c3-f331-6d55-1127-052ff2ee6c56&amp;u=a1aHR0cHM6Ly93d3cuemVlNS5jb20vdHYtc2hvd3MvZ2VucmUvZHJhbWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=11bda34abb67f8d991037ee973fc9a376e3fe9750c4ff0a32320d57299d0d086JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f8a12c3-f331-6d55-1127-052ff2ee6c56&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRHJhbWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ec240af42fd0fc7b6878cacd5e05a9e5a9f5f4e3aa5a3017acdf5c37dc61c635JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f8a12c3-f331-6d55-1127-052ff2ee6c56&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0VlRVF4bTZxY19xYVRFN3FUVjVhTFE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c243b8e83b62983f9e695e01d52e30f42e7810e5716a2df517979171b4c411bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f8a12c3-f331-6d55-1127-052ff2ee6c56&amp;u=a1aHR0cHM6Ly9teWRyYW1hbGlzdC5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e2c77a31407e731371063adbe69dc8bb54929f419081df494d4a5ac3d0186f8dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f8a12c3-f331-6d55-1127-052ff2ee6c56&amp;u=a1aHR0cHM6Ly9odW0udHYvbGF0ZXN0LWRyYW1hcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8dddc8373b8924046807ddcd116e96aeae6748a6584eea89f68a22a6931ca00eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0f8a12c3-f331-6d55-1127-052ff2ee6c56&amp;u=a1aHR0cHM6Ly9teWRyYW1hbGlzdC5jb20vc2hvd3MvcG9wdWxhcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9874a3375daad9d3df71bd8ff41f11e195fcf2fd412572bd533319ac0a643d78JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly9pbi5ib29rbXlzaG93LmNvbS9leHBsb3JlL21vdmllcy1oeWRlcmFiYWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=509a16888924a02c907097fbd54cf2e28f4d415e494f948927913ee2b5be99ceJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly9pbi5ib29rbXlzaG93LmNvbS9oeWRlcmFiYWQvY2luZW1hcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3fee38cb7fe15cb3f37b350c6492e2c9540005c06a1c0a1e51db538d0209415aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly93d3cuZGlzdHJpY3QuaW4vbW92aWVzL0h5ZGVyYWJhZC1tb3ZpZS10aWNrZXRz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3f1a8b6df628a6994fc1eb82fee1a7613786a3e26375d1aad4f0e93bee025d8fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly93d3cuZGlzdHJpY3QuaW4vbW92aWVzL215dGhyaS10aGVhdHJlcy1tZWdoYS10aGVhdHJlLWRpbHN1a2huYWdhci1oeWRlcmFiYWQtaW4taHlkZXJhYmFkLUNEMTAzOTg1MQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c9e47046d4bbb874b7d37ebd18d6ebb652d362dab711ac10d1ed8b76adabc0dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlYXRyZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=67f47c27cbbd2ea830b4addb1fd8fba8107b361ad0dd2bcdfa5ede71d326197fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly93d3cuaHlkZXJhYmFkdGhlYXRyZXMuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9be6ae735c33cc8cf2d38db41db6d56747b6dadfaf33e42cfb135c280613bfd4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly93d3cucHZyY2luZW1hcy5jb20vaHlkZXJhYmFk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0407a2a19787ec257da29c228eae2c257407317fa29e9b34680da92592c5393cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L3RoZWF0cmUtYXJ0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ae04416fdb1d5531cab3f0cdf06e37220e6277f106d430edf910c9b6c31bf59JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly93d3cuaHlkZXJhYmFkdGhlYXRyZXMuY29tL21vdmllcy8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=29ff32e3f4d1ac1fd0a547ae3622e5e1c28d3fa9fd8c282311e09b1f43dcd312JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=081057a8-ce4d-6c63-12d3-4044cfcb6d0a&amp;u=a1aHR0cHM6Ly90aWNrZXRuZXcuY29tL21vdmllcy9oeWRlcmFiYWQvY2luZW1hLWhhbGxzLWFuZC1tb3ZpZS10aGVhdHJl&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d982fc000a0e6c049a9d9d9374ab701fd3099953c161b0f3d406300a9bfbc255JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1479d905-6046-6cc3-28da-cee961e66d07&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NTY0NDU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a32e5692041443c69fbcbaf0f8cde5d8848f788dec7961d78ebe95b13a48f0c1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1479d905-6046-6cc3-28da-cee961e66d07&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1MTk4OTg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3764fed357da96b9d620d952a13bd4ee16b4f6aea0b88106948501fe1b27220JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1479d905-6046-6cc3-28da-cee961e66d07&amp;u=a1aHR0cHM6Ly9hbnN3ZXJzLm1pY3Jvc29mdC5jb20vZW4tdXMvbXNvZmZpY2UvZm9ydW0vYWxsL3dvcmQtMzY1LWFjY291bnQtZm9yLWFuLWVuZ2xpc2gtdGVhY2hlci1mb3JjZXMtYWxsLzBjMmViM2Q3LWRjYzYtNGIxNi1hMzY1LTNjOTIzNWM4NGIwNA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=878e70a2ef5ec19ba99cd2929b7df55efde60a71a7e4cb542bc1f98a38229089JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1479d905-6046-6cc3-28da-cee961e66d07&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NjUxOTA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e8b63f36737520164179d387fdb00594a27cafbc726eda2ff1b4c17dabcc6ebJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1479d905-6046-6cc3-28da-cee961e66d07&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1Mzg3Mzg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d23f1f87b9966dd622ba8a6499aa1e82a7c062dd0d9b5fb4931a0e181199f3cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1479d905-6046-6cc3-28da-cee961e66d07&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NTY0NDk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d2792520ddc9f88c144065610cc492f7f00e352d3adcd43e637eb83c8e06583JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1479d905-6046-6cc3-28da-cee961e66d07&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NDMzODI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d33aca1c688a7e47d98f6ba418501896e5e860266215b54892d3a4da957ce735JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1479d905-6046-6cc3-28da-cee961e66d07&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NDMxODc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4863e38337357d9a01f16dfd11b05e639f89026e5c5e07f08e31415ff42cb7f4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1479d905-6046-6cc3-28da-cee961e66d07&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NjYwODA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=35d022017933ad98d2d611dc8bfac447ac19e7b8c7909ca09064b7a2e89f0e3fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14662aaf-b381-607d-3ed9-3d43b2bf61ed&amp;u=a1aHR0cHM6Ly9tdXNpYy55b3V0dWJlLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6087cb9b249e0c70165d0326dbf278f6fb7e9b42071717c102d4c0025427c291JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14662aaf-b381-607d-3ed9-3d43b2bf61ed&amp;u=a1aHR0cHM6Ly9vcGVuLnNwb3RpZnkuY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eaf1cdbc342f91931ca63a5a22bbe3695a1f42f148989984c54bd1ee7058d658JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14662aaf-b381-607d-3ed9-3d43b2bf61ed&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQy05LWt5VFc4WmtaTkRIUUo2Rmdwd1E&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=962e02227e3c0f4d8155b6b0d5f4bfe6c7b8351a32f4cb6a3d01056d4015e7f1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14662aaf-b381-607d-3ed9-3d43b2bf61ed&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20veW91dHViZSUyMC1NVVNJQw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b703dd6fef483b70381a0e347ca03a40b2138342068b6a076f04611507b461b8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14662aaf-b381-607d-3ed9-3d43b2bf61ed&amp;u=a1aHR0cHM6Ly93d3cuamlvc2Fhdm4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ac3d70acaeed8af15344f873c7b5902740a069262e144751c0e6d74a1d6b287JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14662aaf-b381-607d-3ed9-3d43b2bf61ed&amp;u=a1aHR0cHM6Ly9tdXNpYy5hcHBsZS5jb20vaW4vbmV3&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a826210eabead4342e5072708636870498e921bf607f0e873077296066d91d8cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14662aaf-b381-607d-3ed9-3d43b2bf61ed&amp;u=a1aHR0cHM6Ly9vcGVuLnNwb3RpZnkuY29tL2hvbWU&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c3c4b4089fe01e44b13fbd713e7f24ffc3d6f4ec16916265513d62fdb9229fd4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=14662aaf-b381-607d-3ed9-3d43b2bf61ed&amp;u=a1aHR0cHM6Ly9nYWFuYS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cfcdff9f51b84a384c6212bebec471dd0c843a615e990651cc20d5666207a642JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d097cc3-ba49-6296-3874-6b2fbbc06306&amp;u=a1aHR0cHM6Ly91ZGlzZXBsdXMuZ292LmluLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fc9819fca8dcf904a05ee54429bcf2ff36d01270549dd91beb8a9a511ff3813aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d097cc3-ba49-6296-3874-6b2fbbc06306&amp;u=a1aHR0cHM6Ly9zZG1zLnVkaXNlcGx1cy5nb3YuaW4vcDEvdjEvbG9naW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e77cabcc1fbd876e15784cb2de06659e5903b0d7e08b94526e94adb78034f317JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d097cc3-ba49-6296-3874-6b2fbbc06306&amp;u=a1aHR0cHM6Ly9hdXRoLnVkaXNlcGx1cy5nb3YuaW4vbG9naW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0aebff4e8369af787d1456dfac1c725062ce120d28b301e3e5818c8d625f6adaJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d097cc3-ba49-6296-3874-6b2fbbc06306&amp;u=a1aHR0cHM6Ly90ZWFjaGVyLnVkaXNlcGx1cy5nb3YuaW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98d26e1d0b8752ffb5bdf3b953240fa5f2b08e85a0462aafa21d2187faff484bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d097cc3-ba49-6296-3874-6b2fbbc06306&amp;u=a1aHR0cHM6Ly9zZG1zLnVkaXNlcGx1cy5nb3YuaW4vZzEv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0af25ad1ef3ddd667a6bf23a97db6efcb5275a6004e611f74fcc4062742cfb1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d097cc3-ba49-6296-3874-6b2fbbc06306&amp;u=a1aHR0cHM6Ly91ZGlzZXBsdXMuZ292LmluL2FjY291bnQv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fd2a5a86b2208e6ac27e590c0b9326d0670e77d3c2cc0e7624a7fde9a81efb1dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1d097cc3-ba49-6296-3874-6b2fbbc06306&amp;u=a1aHR0cHM6Ly9wcm9maWxlLnVkaXNlcGx1cy5nb3YuaW4v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7182e2c0e399a7c6aa0d6c4b2a09fcbc94834e50791a3d54ec1ec8162e2778c4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2c99cf5aaa4be0c32ff0934c7110e57ce3ac92cf1bf12172ab3df1d3c7c6dfd1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ed3670de8bf6450a144bc67021618c23b0019bebba14198ea545ef708e3d714JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bbe08b8f2c658054dc6354b4af173d0b07dec2041165bc543f29e25d4e33eb01JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly9zb2Npb2xvZ3kuaW5zdGl0dXRlL2ludHJvZHVjdGlvbi10by1zb2Npb2xvZ3kvY2hhcmFjdGVyaXN0aWNzLWRlZmluaW5nLWNvbW11bml0eS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20687cb2a0a0ebe581c3ad28da731d0d9be21df96ac4e8af18be218c37c57bdfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly9idWRkaW5nc29jaW9sb2dpc3QuaW4vY29tbXVuaXR5Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0de5deba5d3d2acf24d31fc20e5f2b5b2c245eac2110a4b217532d1e4e0fdc0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ca1156cac73e743d10a5bd2e600c32acfedb5a24a935ba911e4705949c25840JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly93d3cuc29jaW9sb2d5Z3VpZGUuY29tL2Jhc2ljLWNvbmNlcHRzL0NvbW11bml0eS5waHA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=756f52bb1aca26c25b61ebe1855db0cedebe760bb926cf82a074e74f04b8bbc0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5XyhUVl9zZXJpZXMp&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ed07e9cb3faab151197ef58bed0b9617ff63a5ee1b95291b5c0ce65390e757aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f410557ea3badc51fada74990c08a48e3b91c0a9bd2ac9d5a69cea668c44591bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1692884b-03c0-600d-2085-9fa7027461bc&amp;u=a1aHR0cHM6Ly9zb2Npb2xvZ3kuaW5zdGl0dXRlL2ludHJvZHVjdGlvbi10by1zb2Npb2xvZ3kvdW5kZXJzdGFuZGluZy1jb21tdW5pdHktZGVmaW5pdGlvbnMtc29jaW9sb2dpc3RzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=18db785946fd2625a8a4a813f20e8b47a73dcc8079a4b39df6cbade543f11973JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWFyY2hpbmc&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3abc748e6056625024c9be9bed60a6e0cbd60b9baf85598b6917de5bd8a039f5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1veTBxNlgyTnVSNA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d8e0ad82efd39adb3975f4b992f07a82ac4b2c66e4e51c28096df72c40b04466JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWFyY2hpbmdfYmFuZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=66a9f81b8f173667122fa0dfe407e0136b4c46670d71d8bddb9e19278af3a4e5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vTWFyY2g&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=08a8ca19c2817f3ed0c96856b6ce8f9d91e61d10bb50a296838be248adbe3db4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vTWFyY2hpbmdEb3RDb20&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c5348b3992741e0c203162877f54374571f54463332a35d6b3e370c7de1b2b15JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL01hcmNoaW5nRG90Q29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f64338fbddb0daed11617f1667f369a93fa9e97f85db3ea5eda904d6d28b9712JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL21hcmNoaW5n&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=056c4775e0efd949a3779197706351df5878891711c98977ef55ccc1064c2889JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly9tYXJjaGluZy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d42942d796a5287386e8d302e62920195b95a8535cecc5f9e67d09de54860440JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vTWFyY2gtSW4tTWFyY2hpbmctQmFuZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3bd873b6ec45e23c6b01596e7bf15f4a76ee4f3770c891ba552943b0a52cb699JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3503875d-47a4-6624-252c-90b146956722&amp;u=a1aHR0cHM6Ly93d3cuc2NyaWJkLmNvbS9kb2N1bWVudC83MTg1NTUwMi9NYXJjaGluZy1CYW5kLUZ1bmRhbWVudGFscw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6865098c6c5ea9aec213f94b604dd1c8df030ed2918ccf6e666668a5baa83a3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzY4MTEzMDc5&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2d894358bef0893ce705b8a2a20f3059c88e7872e3d7cf49a1b8391a2813b97bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3RvcGljLzE5NTYwMDI1L2hvdA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7f1b464a1247141c03645bdabd53da9d1c0dcf3a70db4b77276ea35b24fb53dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly9qaW5neWFuLmJhaWR1LmNvbS9hcnRpY2xlL2MzM2UzZjQ4M2I2NWQ1ZWExNWNiYjUxNi5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1d1fb434cea8fff04b5cdc643cc81de2542201abccb60d97e63ecf39958b0f31JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly9qaW5neWFuLmJhaWR1LmNvbS9hcnRpY2xlL2Q3MTMwNjM1ZTA1YThjMTNmY2Y0NzU0NC5odG1s&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d2bb19a068bfb485d49a634b482a64ee3fecf4eda34d32191774f14616554d25JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzMwMDE1MDkzNw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3cf163fe6687ca39d87978c7e10065869c8dabb24e82994c22d083772ee60697JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzI4MjQ1MzAwNw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7167f1b372527329e6810f2ed9ea49eaadb512df0fe283bb6b9066e84a5c38f0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIyNDMyMTAy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9e6de3007ac4d900346ae2e062460b76bbb8afcf95d113b1f81fa2329cc22cbdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzIwODcxMzYw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=081212ebbb82fb4aca427547d4c24af60eefbe1936b78dd5d46d60b518c0dd0cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzMxODc1MDcx&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4680200861dd4abad6f05ad22e6a1f8c6850c1c0d617c0d5d0a3c392928cbc91JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=33db9bb8-04f7-63ad-23f9-8c54052562d8&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzU1NDg4NTU0Ng&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e787fa409df52cecaf085ca9aee1ea61a656dd281eee64a2e44fe8796c3a5634JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=2ebb20c3-fb11-6417-0a9a-372ffa3b65d0&amp;u=a1aHR0cHM6Ly90cmFuc2xhdGUuZ29vZ2xlLmNvLmluLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ca9924b4b3fb8336dfc43f1532e549f6104aa9071f9cb722f12fb81a6aa7d28cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02c85fe3-f4df-67d0-2310-480ff56d6616&amp;u=a1aHR0cHM6Ly93d3cuaXEuY29tL2RyYW1hP2xhbmc9ZW5fdXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4daedc4a8a1ce8534fbc186fde4455062905b33429c04b40eab2ea74c6dcf07JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02c85fe3-f4df-67d0-2310-480ff56d6616&amp;u=a1aHR0cHM6Ly93ZXR2LnZpcC9lbi9leHBsb3Jhcg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ccdda19ab99fd09f7dc61e704be52db063034d89504e91ea99f53c91314a1baJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=02c85fe3-f4df-67d0-2310-480ff56d6616&amp;u=a1aHR0cHM6Ly93d3cuemVlNS5jb20vdHYtc2hvd3MvZ2VucmUvZHJhbWE&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2a7003127338f69b8880a6a17ee9e1f2eee2379603baf97c1739a5c3b3168191JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNDA5Njk3MTAvZXJyb3ItNTcwLWFkaGFhci1lLWt5Yy1hdXRoZW50aWNhdGlvbi1hcGktaW1wbGVtZXRhdGlvbi1pbi1waHA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb426510033f31ecdb4a0582a9e4be6634b54678ef2cf33eae60aa15bcbd1605JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNDg5MDQ0MTcvaG93LXRvLWludGVncmF0ZS1hYWRoYWFyLXZlcmlmaWNhdGlvbi1hcGktdG8tamF2YXNwcmluZy1tdmMtd2ViLWFwcGxpY2F0aW9uLWZy&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f868c39b437747aeaccde0aab7bf7f65fb0312570d964f3b02305516eae9d8aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNjI2NzYwMTEvaG93LXRvLXVzZS1hYWRoYXItYXV0aGVudGljYXRpb24tYXBpLXVzaW5nLW90cC1yZXF1ZXN0&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9d733d10f85b8df84abf069c8b6a6f997b45c7c62ed4bf0971544b8f58b7aa8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvMzEzNzcwMTUvaG93LXRvLWludGVncmF0ZS1hYWRoYWFyLWNhcmQtYXV0aGVudGljYXRpb24tYXBpLWZvci1hYWRoYWFyLW51bWJlci12ZXJpZmljYXRpb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=56e492454e80d9be5b4dacec29319c1fc41e1e77086aff0e69b4e0927e11eab4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNzcwNTEzNjgvaG93LXRvLXBlcmZvcm0tYWFkaGFhci1la3ljLWF1dGhlbnRpY2F0aW9uLXZpYS11aWRhaS1hbmQtcmV0cmlldmUtdXNlci1kZXRhaWxz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed1316f8f37fd4df9d74eb648ff4ef3d3deb05d0888544c710a5d40cebfc5c1aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNDIyMDMzODAvaG93LXRvLWltcGxlbWVudC11aWRhaS1hYWRoYXItYXBpcy1pbi1hc3AtbmV0LWMtc2hhcnAtYW5kLWFuZHJvaWQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52b5cfda3ee8ae4b11407a69e4b19e006e80cc0978750aad9738a01b5df5dc5aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvMzUxNzcwOTUvaXMtdGhlcmUtYS13YXktdG8tY2FsbC11aWRhaS1hYWRoYWFyLWFwaS1mcm9tLXBocA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eeff2b3c05c7343da8a441ce38b814b5fb9f3a1bd7f9075f3a59711f74d0e059JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvMzA5ODYzNzYvaG93LXRvLXVuZG8tYS1zdWNjZXNzZnVsLWdpdC1jaGVycnktcGljaw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ed3c5ad63472c57ee42305c71432d91cd0f3a04163d581b4d629f1164c9cf106JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNDIzMDY0MTAvZ2l0aWdub3JlLXN5bnRheC1ob3ctdG8tZXhjbHVkZS12aXJ0dWFsZW52LXN1Yi1kaXJlY3Rvcmllcw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d17f9cf6d79beb24a3b62c58c6960211673961994250aedc06d50c4c879fa796JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0b05b00f-acc4-6557-1301-a7e3ad4264f5&amp;u=a1aHR0cHM6Ly9zdGFja292ZXJmbG93LmNvbS9xdWVzdGlvbnMvNDM4NTU0MDQvZXhjZXB0aW9uLWR1cmluZy11aWRhaS1hdXRoZW50aWNhdGlvbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0eaf0443aee1b74a3e3da68bb36efa2c409624786a315847c945169b04b441a9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly9lbi54Y2hpbmEuY28vbW9kZWxzL3R5cGUtNC8xLmh0bWw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5652ed581b61129b897a3b082b3903475495e32c5997e5ae4593c1abf0ad370aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly9oYW5pbWUudHYvcGxheWxpc3RzL2ttZ2U2azhieTRjbnY0enR3Z2ts&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3580c1e754a442bd26eca3fc8979c6d3280a96707d16894204b429b5e83fb6b6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly93d3cuY3BvcGhvbWUuY29tL2RyYW1hLXRhZy9zZXh1YWwtY29udGVudC8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7bd40376c2f6a126f46fadf012b64de5d90824f5e6742e14d04bbcb7e5fcc49aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly9jaGluYXVuY2Vuc29yZWQudHYvY2F0ZWdvcmllcy9jaGluYS11bmNlbnNvcmVk&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d131280a8e024e49a47a28b3ed77ca6fb20c33a0844aae4e6e1e45210af97d77JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly93d3cuaW1kYi5jb20vbGlzdC9sczA0NTI5NTY3NS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81e8a944390853b96a651105504f74be76f878805a18a3b24987a5f041e88191JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly93d3cuc2NtcC5jb20vdG9waWNzL3NleC1hbmQtbG92ZS1jaGluYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0bc78f17d5b257958f0c807726913f8c8f6b4d13ea96af40081f0b7f4874eee5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly93d3cucm90dGVudG9tYXRvZXMuY29tL20veHh4L3ZpZGVvcy8xODI4NzAxMjUxOTk3&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fcc90ea85089771060efa51c55928a727041d6a66ed79df4ab6917c71407940dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly9waXhhYmF5LmNvbS92aWRlb3Mvc2VhcmNoL2NoaW5lc2Uv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c8fb968a47b0aed3c11abf957d545ce372a05b68d8ed891049d97f58cc0872aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly93d3cud2hhdHNvbndlaWJvLmNvbS9zZXgtYW5kLXRoZS1jaXR5LXdvbWVucy1zZXgtaW4tY2hpbmEtbGl2ZWJsb2cv&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d33713a096792c6b6b6d7c6e202b4544ead2d78c24ed72d1ec72904388d071f9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=133239fa-5bf8-687f-04e4-2e165a1969fa&amp;u=a1aHR0cHM6Ly9jaGluYWZpbG1pbnNpZGVyLmNvbS90YWcveHh4Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96b71eb4e376785e3a71cf2454887bd836b5c7d129b4b55d1a85dbb4de2cd536JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly93d3cuaXJvbm1hbi5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb1cf2a3cacdbd267ab914d24c36ea2fa95e9fc3fc7f64b88a644e6bc56366c8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly93d3cuaXJvbm1hbi5jb20vaW03MDMtd29ybGQtY2hhbXBpb25zaGlwLTIwMjYtYW5ub3VuY2VtZW50&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3517fe999c11546ca721b0812f02c2efd4f62182741175edf872b399a78e0d46JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly9teS5pcm9ubWFuLmNvbS9zaWduSW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ca2a011e4856e7048561938a61c19f6947eed7d4c0c25f398e3af7292e82f36JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly9teS5pcm9ubWFuLmNvbS9rYi9hNTgyZDQ1OS1lNjRmLWU5MTEtYTk3Ny0wMDBkM2EzNzQ2OGM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a184713b183f3d35b56442de89219dae19ed7559d7cb0ff8e8e9e9e11c63a039JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly9yZWd1cy5pcm9ubWFuLmNvbS8&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea3117bf5656271b9bbff6b37fa5daf0143016329ac6220b3e8f84fd15d8c2baJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly9yZWdpdGEuaXJvbm1hbi5jb20vZXZlbnQvMjAyNi1pcm9ubWFuLTcwMy1pdGFseS1lbWlsaWEtcm9tYWduYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=535294079c0e5031b2d1ab754a9cfa56a24d83598e9c94407c9561b53bebbba4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly9yZWdnYnIuaXJvbm1hbi5jb20vZXZlbnQvMjAyNi1pcm9ubWFuLXdhbGVz&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f5981c7645301fc920f334918fc102cb431725dcd28c0e424c4b2f7bff05878bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly9yZWdkZXUuaXJvbm1hbi5jb20vZXZlbnQvMjAyNi1pcm9ubWFuLTcwMy1lcmtuZXI&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6670eef1cec601fbf460a454e73900fd316529de7b2ca5d5c6dcf162ac21117bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly9wb2RjYXN0Lmlyb25tYW4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=38fce81ee4a4114175c0c70390cf7f3e44de36c8977f25475ee6c52428145b13JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=03bdd21f-cc44-6b49-2f0a-c5f3cd566a26&amp;u=a1aHR0cHM6Ly93d3cuaXJvbm1hbi5jb20vcmFjZXM&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f46466bb8f16a09d14279cdf8e983cb5643524eaea2ba847568b72324c1b167aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=38670a8e-9098-66f4-1131-1d62914b67e4&amp;u=a1aHR0cHM6Ly9hbnN3ZXJzLm1pY3Jvc29mdC5jb20vZGUtZGUvc2t5cGUvZm9ydW0vYWxsL3NreXBlLWFjY291bnQvYzM2OTllMzctMjU1NC00NjIwLThmMTAtZDBkMDNhMThlNDM1&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a00e5fc21ca116a65b0e3a3389a46727670276809ef1c44c7434f715560d08bcJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3a938ec1-10c0-6647-0504-992d11d467cf&amp;u=a1aHR0cHM6Ly93d3cuamlvc2Fhdm4uY29tLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7c63c641ce503a6da8ca0d5d0906fb3d9300144f19cf89d8bd1e32130ba4ab6fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15b24dd0-7d2d-65f2-13b1-5a3c7c2264f0&amp;u=a1aHR0cHM6Ly93d3cuc2xiZW5maWNhLnB0L2VuLXVzLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ccb44d6c4275f86b2c890a370fa0b2e2d7b755b8e90019046bdba0d70ee464fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15b24dd0-7d2d-65f2-13b1-5a3c7c2264f0&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvUy5MLl9CZW5maWNh&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3501fdb2fb83368b6bc300b4b04d14c255bdef4c8da9407fbc111aa077177d7bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15b24dd0-7d2d-65f2-13b1-5a3c7c2264f0&amp;u=a1aHR0cHM6Ly93d3cuc2xiZW5maWNhLnB0Lw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=059ae87eb7e386e6f0fc08b90c5d1aca37c74065f9e3e2b4402d22074afa72d1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15b24dd0-7d2d-65f2-13b1-5a3c7c2264f0&amp;u=a1aHR0cHM6Ly93d3cudHJhbnNmZXJtYXJrdC5jb20vYmVuZmljYS1saXNzYWJvbi9zdGFydHNlaXRlL3ZlcmVpbi8yOTQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0394382811ae58635eaa06ddd70682e09a68458a57bad8a0bf532ac782819a48JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15b24dd0-7d2d-65f2-13b1-5a3c7c2264f0&amp;u=a1aHR0cHM6Ly93d3cuc29mYXNjb3JlLmNvbS9mb290YmFsbC90ZWFtL2JlbmZpY2EvMzAwNg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=639b1cd0a6a46c598eeb521b62bb964b71011787523c89b89168ec0b0c655778JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15b24dd0-7d2d-65f2-13b1-5a3c7c2264f0&amp;u=a1aHR0cHM6Ly93d3cudHJhbnNmZXJtYXJrdC5jby51ay9iZW5maWNhLWxpc3NhYm9uL2thZGVyL3ZlcmVpbi8yOTQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=47abd5cf54ce6b23b5464669cd58c94935d58aab11415e4ffef892c945b23b1eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15b24dd0-7d2d-65f2-13b1-5a3c7c2264f0&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvMjAyNSVFMiU4MCU5MzI2X1MuTC5fQmVuZmljYV9zZWFzb24&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=94851d6b38e7850b160c77330001d2b486935094f8c1e4713f2fc42543ea2f27JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15b24dd0-7d2d-65f2-13b1-5a3c7c2264f0&amp;u=a1aHR0cHM6Ly93d3cud2lraXdhbmQuY29tL2VuL1MuTC5fQmVuZmljYQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e396a683a8faa2694e8af7f43693c4f005185896631b8b43ff2b5b06167200acJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=15b24dd0-7d2d-65f2-13b1-5a3c7c2264f0&amp;u=a1aHR0cHM6Ly9zbGJlbmZpY2Eub3JnLw&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=16cb41ee2926a1728373543178cb994ade7e04a175a293f2afb06da40b4300e4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0cdb40ec-656d-6d1b-0530-570064e86cf0&amp;u=a1aHR0cHM6Ly9mci5zaG9wLW9yY2hlc3RyYS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f9c03395e57de123a021dac557db050d5ea6252e4e63029b0effd2132121da51JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci85NTM0Nj9obD10ciZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=678ecebcee5e46dc66ec065b35ac5c7bfd94ba945759eb2724a0f56ca6b2be1dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci85NTM0Nj9obD1odSZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=09d68d9ed90455ea2ca2732c5b6683e5fc4940e51bd0b2425bea9c14e24f3537JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci85NTM0Nj9obD1rbyZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f1d33d061e31128016cc8c472b512401810441902e40d988f625b39e83e28728JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci85NTM0Nj9obD1oaSZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d4069279e352fbfe9fd537cc995722e0fb6f7ff1947a3cc988cb2dbaf74807d8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci85NTM0Nj9obD1mciZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0cba52649ae12f204d47ce5928d74da0966554495603d99a2f93bddf1560c810JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lLz9obD1pZA&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc7cfef2771e3f9466647f3d5ef9ba0c7cbca8fa82d397f0b1a0652587613f11JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lLz9obD1lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0ca6ad992f61af5bcb2f9677622a8e2472b645b08100b2ffc136e4d3f2dc44d5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci8xNjczNzYyOD9obD1lbg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dacd4a8e7212c9d5575606492fe63380b106568bd3d7124cbdf90643c9008bf1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci8xNjczODM0ND9obD1wdC1CUg&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ffa628b93dfe0b1356c4679c3536eeac0340a2e1f69fb2a31a92f85170d8f4b3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37df0b83-6853-6b3c-3360-1c6f69dc6a61&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20vY2hyb21lL2Fuc3dlci85NTQxNz9obD10aCZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5f5424c8059c58ea8f42b0f49ebd8a2e9ada79f181308adc54a8605f2d3ad255JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1242a2da-0e4c-61e4-2311-b5360fad603d&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1370aa29c23de8bba26e6e7a31b962e6672596b86b22e3150608a7e4b60628f7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1242a2da-0e4c-61e4-2311-b5360fad603d&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20veW91dHViZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6eca5b4cbf62493c5e865f0c6d9d69109c8f7f4ebb680c8a7eddb5edecc6affdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1242a2da-0e4c-61e4-2311-b5360fad603d&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvWW91VHViZQ&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b65ed317fde9e197412cbdeba0e5aac05a4758c42aaed814fa461ee990ee62baJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1242a2da-0e4c-61e4-2311-b5360fad603d&amp;u=a1aHR0cHM6Ly9wbGF5Lmdvb2dsZS5jb20vc3RvcmUvYXBwcy9kZXRhaWxzP2lkPWNvbS5nb29nbGUuYW5kcm9pZC55b3V0dWJlJmhsPWVuLVVT&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4ccf3a24b061171fe38e55e78df858aa67fddd52537def6befee260cd9f12c34JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1242a2da-0e4c-61e4-2311-b5360fad603d&amp;u=a1aHR0cHM6Ly93d3cueXQtaW5kdXN0cmllcy5jb20v&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b831d2039145c08df704fb2bea46497b8fec0c0094be998bab5674aa193b39cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1242a2da-0e4c-61e4-2311-b5360fad603d&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS8_aGw9ZW4&amp;ntb=1</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e1c68df1e407093e94c5a01016f55b4c0ebb54dfcfd696876af34640b828d207JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1242a2da-0e4c-61e4-2311-b5360fad603d&amp;u=a1aHR0cHM6Ly9hcHBzLmFwcGxlLmNvbS91cy9hcHAveW91dHViZS9pZDU0NDAwNzY2NA&amp;ntb=1</t>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=21fd7dfa5649eb1eb3540326cc66e60d17763cc37f4dd24ff0686c03326707ecJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ2hvaXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3ad10c3eef028969a097847443a4319c68575986cb7108bdfc9381d7eaf59366JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L2Nob2lyLW11c2lj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=057bf95d87722bc75663daaf2737df6c75073859c42f11255eeef4b81a4b1444JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly9sYWdnZWQuY29tL2VuL2cvY2hvaXI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=de34ef32baa92c11f57f13a018f221bae9ec235e08d9ff77bd1edef29317854dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2Nob2ly&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4851335639f54384163b0c1a850410c7b557203ecd181a1499476ff1d99745f7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly93d3cuY2hvaXJzY3JpcHQubmV0L2Jsb2cvd2hhdC1pcy1hLWNob2ly&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ebd747c63bf16fcd3ff21f9dc9b2c49cfeb5296c96e411eee6a2846683b2877eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2Nob2ly&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9274d44257b712e40b551be7d47a34b35de7fb19ccc2592f663b0842e37cbadfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL0Nob2lyXyhtdXNpYyk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8bc14d901c73b0a613beb6d46a203b5cd36c56c17445b45a1457f567b41d8cc4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj0zQ25Ld2RtLS1JTQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52853ee8a74da89186132e1daea8874ddb34e5af5e8aaa76bd50f318115f698fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2Nob2ly&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6bef7a237dddbe0a4d04382649db2cd878ee4b010aad61213d6b3b4ae8176c7eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3de3e4c7-b241-65c0-12a2-f32bb34e64a7&amp;u=a1aHR0cHM6Ly93d3cucm9ja2V0Z2FtZXMuaW8vZ2FtZS9jaG9pcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=30483b9a318f03c7ca920147ee26514ba804ed951f837c2b9643f09886cb5b70JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27bf181b-f9cb-6ad2-06f7-0ff7f8df6b49&amp;u=a1aHR0cHM6Ly93d3cuYmFuZC51cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d45fbb5d4ee800634da4c68cffffb020a9fb34a4110d1becbbef7e04168f15cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27bf181b-f9cb-6ad2-06f7-0ff7f8df6b49&amp;u=a1aHR0cHM6Ly93d3cuYmFuZGxhYi5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6ddc67e462fe10593787ca8bb9dc882664c6c320ce24d5f4f6b6f992cd3dc677JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27bf181b-f9cb-6ad2-06f7-0ff7f8df6b49&amp;u=a1aHR0cHM6Ly9wbGF5Lmdvb2dsZS5jb20vc3RvcmUvYXBwcy9kZXRhaWxzP2lkPWNvbS5uaG4uYW5kcm9pZC5iYW5kJmhsPWVuLUlO&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=95e436bb99197c1f8dde31435731f0d15061cab92de1236eb67e7b9304be210dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27bf181b-f9cb-6ad2-06f7-0ff7f8df6b49&amp;u=a1aHR0cHM6Ly9hYm91dC5iYW5kLnVzL2ZlYXR1cmVz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e65c16b02a7b7f4aba7087271e5af3c626d465474fc85aee5721b2ead959b584JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27bf181b-f9cb-6ad2-06f7-0ff7f8df6b49&amp;u=a1aHR0cHM6Ly93d3cuYmFuZGxhYi5jb20vc2lnbi11cA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=07950d07256ea754e97ce40805772547afa3682ba80fcf0477814bc694fbace7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27bf181b-f9cb-6ad2-06f7-0ff7f8df6b49&amp;u=a1aHR0cHM6Ly9hYm91dC5iYW5kLnVzL3Jlc291cmNlcy90dXRvcmlhbHM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8a55270b8a119a7bbdfe5120aa15d368bbe7ebd0df9ea7556eaf790870132d92JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27bf181b-f9cb-6ad2-06f7-0ff7f8df6b49&amp;u=a1aHR0cHM6Ly9hcGtwdXJlLmNvbS9iYW5kLWFwcC1mb3ItYWxsLWdyb3Vwcy1hcHAvY29tLm5obi5hbmRyb2lkLmJhbmQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a7e2c7a55b0eb141496477e47de8c20a1ceaec465e45593845964aed8f5e419dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27bf181b-f9cb-6ad2-06f7-0ff7f8df6b49&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQmFuZF8oc29mdHdhcmUp&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e51e2b3a72e068f5466b7e31a65a94451d2a2a5a407682867df1e7a42499fccfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=27bf181b-f9cb-6ad2-06f7-0ff7f8df6b49&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vQGJhbmRhcHA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=74300db829a61438c3b76091f1aa0e3565e79251c2b13562e9073a2f2c9e2da7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvT3JjaGVzdHJh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2686d2209476de50aac33b0877ef5e642fb31539cc82697ffef7a331e407d8daJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L29yY2hlc3RyYS1tdXNpYw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d0e7cba4be2411f6a6f234ee9fef3c2b83606c710ec67ff07737207f0ab1d6a2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly9hbGxldmVudHMuaW4vYmFuZ2Fsb3JlL29yY2hlc3RyYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2847f6e5e4d9535250af64571c818cc800545a334e94cc3bac17dc4cb642f391JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly9zaW1wbGUud2lraXBlZGlhLm9yZy93aWtpL09yY2hlc3RyYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=671d89cdf72f8130d5f403a0bbd02d88b7305729ee2055e09a112cf3b7e15d19JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly9wcm9tdXNpY2lhbmh1Yi5jb20vd2hhdC1pcy1vcmNoZXN0cmEv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=63a1290b2652296e15569a7505de5294b34bc0fd9521fa6a6386929a11fefd00JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly9mci5zaG9wLW9yY2hlc3RyYS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f0c962ae30c54cf06c6a3997d8ccd615e4c0fec226850c3e88f6ec036e87bddfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj04dG1HSjUyUEJjVQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=df5ead219d71e17fe0340ff61174a3adc41cd0fa0f7b3e708433dda69ba22f61JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly93d3cud2lraXdhbmQuY29tL2VuL09yY2hlc3RyYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=83dcf91e27be919dc3f423fadc75ac28d0def7e8576c433158e8e382af56415dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vcGxheWxpc3Q_bGlzdD1QTEU5REVGODk4QkNDNUE0NzY&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9337fc7d89dfa7ae6b79081b99e9999343c343bf6fc8bfce6513b8ff40670b7dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=250fb14f-1016-6a50-266c-a6a3117d6bba&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL29yY2hlc3RyYQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a2f90662a45a7d2ea31dc8033966f9ad422cf56d5c7af05515e6d8f69747f8d0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=040a8103-9041-6f48-39c6-96ef91c96ef8&amp;u=a1aHR0cHM6Ly93d3cuaXEuY29tL2RyYW1hP2xhbmc9ZW5fdXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4262b1ea2af154a57ddc9799c0e194b0ff4080eba7fdf9f7e59ce6a437af5a67JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=040a8103-9041-6f48-39c6-96ef91c96ef8&amp;u=a1aHR0cHM6Ly93d3cudmlraS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b9a7e8ab441960c3d10e321146b931db2d33ef2adb7842415c7f550b3b80c431JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=040a8103-9041-6f48-39c6-96ef91c96ef8&amp;u=a1aHR0cHM6Ly93ZXR2LnZpcC9lbi9leHBsb3Jhcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=24b28b5e5830161605bbc9ca83cc75d28657b6c0d70ea525e61e1413b2a9e5c1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=040a8103-9041-6f48-39c6-96ef91c96ef8&amp;u=a1aHR0cHM6Ly93d3cuemVlNS5jb20vdHYtc2hvd3MvZ2VucmUvZHJhbWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1fe694010ee50e39e26acdde04a1346f56dfc2dab1f7b758318ecae8de3f4101JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=040a8103-9041-6f48-39c6-96ef91c96ef8&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvRHJhbWE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1f68de4c3df699d73b82174133f544597393ce60dc312be0019a1d2497ccd411JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=040a8103-9041-6f48-39c6-96ef91c96ef8&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQ0VlRVF4bTZxY19xYVRFN3FUVjVhTFE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6bb0fa87000bf0984b76421e99fcd2699f8d20bfe7fe91808a7e8a3548687b42JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=040a8103-9041-6f48-39c6-96ef91c96ef8&amp;u=a1aHR0cHM6Ly9teWRyYW1hbGlzdC5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4f5fb0394689c39d84ace6a2422c02875ab8f4552532b582a8c1eb3935d189cdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=040a8103-9041-6f48-39c6-96ef91c96ef8&amp;u=a1aHR0cHM6Ly9odW0udHYvbGF0ZXN0LWRyYW1hcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e9bb5ab70f33220509bdae80452876029c2105de97cb70ae9829935f2077cc7fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=040a8103-9041-6f48-39c6-96ef91c96ef8&amp;u=a1aHR0cHM6Ly9teWRyYW1hbGlzdC5jb20vc2hvd3MvcG9wdWxhcg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e062186ccaccec9f5c6e518d8fe40fbbcbb1f0dbe9eb1c767fe9def04c873aecJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly9pbi5ib29rbXlzaG93LmNvbS9leHBsb3JlL21vdmllcy1oeWRlcmFiYWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=54e9dd196e4b7673048f1488fbaa0480fc16137a2c2542dd2afeddaf3cc544c5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly9pbi5ib29rbXlzaG93LmNvbS9oeWRlcmFiYWQvY2luZW1hcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e659aa7a2aa34c31e75151887428c2630c03609a317c34ad73943208d2713baaJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly93d3cuZGlzdHJpY3QuaW4vbW92aWVzL0h5ZGVyYWJhZC1tb3ZpZS10aWNrZXRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8332bceacbd71d9ddf09317fa483f83b447dd1660176d9f29e181c1646cbe311JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly93d3cuZGlzdHJpY3QuaW4vbW92aWVzL215dGhyaS10aGVhdHJlcy1tZWdoYS10aGVhdHJlLWRpbHN1a2huYWdhci1oeWRlcmFiYWQtaW4taHlkZXJhYmFkLUNEMTAzOTg1MQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e3caf0a8c8d79b2c11ff4da18c5683f83fd5f17a7b897b6634a8dbd53733940cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvVGhlYXRyZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82409bfeeb93d66309c19729970e3ca8d0c61b412d75f8f3325eae5bed1e24c9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly93d3cuaHlkZXJhYmFkdGhlYXRyZXMuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=67b4029a7f9ad700b88ed86bb5513f33b7f68b50988a19b1482ab1b654bc8e64JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly93d3cucHZyY2luZW1hcy5jb20vaHlkZXJhYmFk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=75ea3ff5f352aee5ce93b35125dbe10e033dfbc65e19a1e73019028a2b87cdbeJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly93d3cuYnJpdGFubmljYS5jb20vYXJ0L3RoZWF0cmUtYXJ0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=62fb71a798831aa5a8173ed98789b85171849e734287a70be2847e5e1c5c4904JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly93d3cuaHlkZXJhYmFkdGhlYXRyZXMuY29tL21vdmllcy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a445e7d5eed03e8aafd0a6df536f054888eee735b740ce0a03cf80fc0668abbcJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1792a662-64b6-674b-0515-b18e65dc66ce&amp;u=a1aHR0cHM6Ly90aWNrZXRuZXcuY29tL21vdmllcy9oeWRlcmFiYWQvY2luZW1hLWhhbGxzLWFuZC1tb3ZpZS10aGVhdHJl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d007446e93bc6839a61f2386bdde9f4b069a04b2ad7437cb054c410a3f41a99fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly9kZXRhaWwuY2hpZWJ1a3Vyby55YWhvby5jby5qcC9xYS9xdWVzdGlvbl9kZXRhaWwvcTExMTgxODY0Mjc2&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d10202f337a36a753d21e74d310a60fab00332adedea38b2c1593f8eeb8cd0bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2ZyZWVwYXR0ZXJucy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7297af600e15ba326a8272684e7390d94bb89bd87341ca0746e041797f6bdda9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly9kZXRhaWwuY2hpZWJ1a3Vyby55YWhvby5jby5qcC9xYS9xdWVzdGlvbl9kZXRhaWwvcTEwMjczOTM5NTIw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=05b27e28ba46da8969676eb8c23b8175836de68c2b5ab65e864ef119305d696eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3BkZi9jb21tZW50cy9wZGwzOWIvaV9sb3ZlX3BkZi8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=60c5ecbc836f662624824ca21aab26a497d9252f57a69ca928d80503295088d2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzQ3NzgxOTc1NQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=841b7644a1e5670aea4e9b4ab17090f227d2fe853f71a161544cdd9608d5e101JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzUwNDU1MTE5MA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c981fca0a609463c187150f88d07264d7a27a632befdd17b26d0da20385ff6abJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL1VDU0MvY29tbWVudHMvaGk4d28xL3RoaXNfaXNfc3VwZXJfcmFuZG9tX2J1dF9pX3dhbnRfdG9fc2hhcmUv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b6666e0a6303694d0c061cb73334e8741dbc9aada4ea02d96cb2eec609f1fb15JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0FQRXVyby8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b42bf5b49df0fa2d2839d1e54124a0f34ee5e745723f1de85aec0f70c4bcc8adJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL3JlZGRlYWRyZWRlbXB0aW9uL2NvbW1lbnRzL2J1eGp1di9jb21wbGV0ZWRfYXJ0aHVyc19qb3VybmFsX3BkZl9hbmRfemlwLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5ec2db96365f2edab3c618ef97cfae051caf89196bbadd81efe06d6e72a6f348JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=10449c38-6359-6f8f-3a8c-8bd462ca6ee3&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL2thbGltYmEvY29tbWVudHMvZzNtOWVhL2h1bmRyZWRzX29mX2thbGltYmFfdGFic19hbmRfc2hlZXRfbXVzaWMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8f12549e62a6aea29eab743ffff83412fdfd40ca41162bb7f0f67e0c494a3f99JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d1423f-325d-68d9-3592-55d333dc69fd&amp;u=a1aHR0cHM6Ly9tdXNpYy55b3V0dWJlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa9a56e6e936992f55156b62b09f4f39c590ba2aec61708a2ee03c73041909a8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d1423f-325d-68d9-3592-55d333dc69fd&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vY2hhbm5lbC9VQy05LWt5VFc4WmtaTkRIUUo2Rmdwd1E&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9109aedb15e34e1015287e5adb7ca76a77113235dfc5d2a1b0d2e5f40cba106JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d1423f-325d-68d9-3592-55d333dc69fd&amp;u=a1aHR0cHM6Ly9vcGVuLnNwb3RpZnkuY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6cccd30056487b40e5e29b01b1ae5f9cd2f6a10b0e096e710872e659cbd93742JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d1423f-325d-68d9-3592-55d333dc69fd&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20veW91dHViZSUyMC1NVVNJQw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e32a61f5af1c0055e5a4adef46a0b201aef1a2d0b882b1053217ab507dc3e5e5JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d1423f-325d-68d9-3592-55d333dc69fd&amp;u=a1aHR0cHM6Ly93d3cuamlvc2Fhdm4uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e29f5e587a0de8e7a4ecaf374fb669e33526ffdbd75a9109409a1c4029a6097JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d1423f-325d-68d9-3592-55d333dc69fd&amp;u=a1aHR0cHM6Ly9tdXNpYy5hcHBsZS5jb20vaW4vbmV3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=81aa78969c72c629475ae3f46ecbbcfea3e4a99ad4b87cc72da126e0e66c0084JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d1423f-325d-68d9-3592-55d333dc69fd&amp;u=a1aHR0cHM6Ly9tdXNpYy5hbWF6b24uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a03295e58c933bc623d2118122c7438ed9e179541bcb59df88ce54538f5bfcc1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=32d1423f-325d-68d9-3592-55d333dc69fd&amp;u=a1aHR0cHM6Ly9nYWFuYS5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=da11380837d4df2fcf5d7620ed80aa3a1897c7ca61d1411d4fafc80e614bac3cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=330c2dcb-4808-6c3c-3855-3a2749226dfe&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NTY0NDU&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=52887bd3c0cfd6de5bb36233afd4f783185cd687cbde01e64db2a50df195d9e9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=330c2dcb-4808-6c3c-3855-3a2749226dfe&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1MTk4OTg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=fb3f4497b50a9fd9d9a0acdc306b3412c2051c60298df377cbf87ddaaed7d52eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=330c2dcb-4808-6c3c-3855-3a2749226dfe&amp;u=a1aHR0cHM6Ly9hbnN3ZXJzLm1pY3Jvc29mdC5jb20vZW4tdXMvbXNvZmZpY2UvZm9ydW0vYWxsL3dvcmQtMzY1LWFjY291bnQtZm9yLWFuLWVuZ2xpc2gtdGVhY2hlci1mb3JjZXMtYWxsLzBjMmViM2Q3LWRjYzYtNGIxNi1hMzY1LTNjOTIzNWM4NGIwNA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6da77751eeb82a6cf628dec01a130890243863576b7043ca8e04b9969de861efJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=330c2dcb-4808-6c3c-3855-3a2749226dfe&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NjUxOTA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7efddf800d56e7e62e0994a55267b490d4f1a2bf2dda95989321dbc44e16562JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=330c2dcb-4808-6c3c-3855-3a2749226dfe&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1Mzg3Mzg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e8053b62fe2563609651bf1f059ae705134c9f20b9c76a2287238b2530649362JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=330c2dcb-4808-6c3c-3855-3a2749226dfe&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NTY0NDk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8e7b60378a070044d5ca8eeca1815d8377c9f7e5519222bb20ec03cdde84fe89JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=330c2dcb-4808-6c3c-3855-3a2749226dfe&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NDMzODI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c0cff2cd6cbf1a9a3439bb474449af425317edcf3e0e77139bb8e32156088626JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=330c2dcb-4808-6c3c-3855-3a2749226dfe&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NDMxODc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=963a5f7b516b4f9ec07d3fc5530105961820fed35932293d879814a04e994eebJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=330c2dcb-4808-6c3c-3855-3a2749226dfe&amp;u=a1aHR0cHM6Ly9mb3J1bS5sb3d5YXQubmV0L3RvcGljLzU1NjYwODA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7edbaedaf272c94c20ad56bcb4de63077db46bdcad3499db7d04e1736ea37935JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=eee5b681db5382f13084f00ac51ee763e732a549061d4b20ee6550ceb846f306JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly9wdXJlc29jaW9sb2d5LmNvbS93aGF0LWlzLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=86e04e0db2cd1b1527e2a223fb2f0d889eec4030e1f6d5cc6265eac9a7e18776JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly93d3cubWVycmlhbS13ZWJzdGVyLmNvbS9kaWN0aW9uYXJ5L2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0235a0bb352e88962cb9ca8028c730e02fdb96fbd966663d58fa4abe3a080f43JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly9zb2Npb2xvZ3kuaW5zdGl0dXRlL2ludHJvZHVjdGlvbi10by1zb2Npb2xvZ3kvY2hhcmFjdGVyaXN0aWNzLWRlZmluaW5nLWNvbW11bml0eS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f3d687df170699444a91814bd59d0deffc1b30b4330df7d838dce986940633a3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly9idWRkaW5nc29jaW9sb2dpc3QuaW4vY29tbXVuaXR5Lw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6aa48442da22d54828afd41d1d9a6e7a03346ee9cafae810b3d28dce183b965eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=aa59393d3d4a618b20df14c874befb09e7e5953cf2235c54cf1cf024df420afaJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly93d3cuc29jaW9sb2d5Z3VpZGUuY29tL2Jhc2ljLWNvbmNlcHRzL0NvbW11bml0eS5waHA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c796cfe24852649df16d1f8ee640f6a07ae6d4d75e8a26517417be517b190a90JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvQ29tbXVuaXR5XyhUVl9zZXJpZXMp&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7a113a5c28cd43ce0cd9aa92854f3d81c4e00f23f48309794f363d0f57f8d7d7JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvdXMvZGljdGlvbmFyeS9lbmdsaXNoL2NvbW11bml0eQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d56ffa21e53cc2d6f3202a782e5c891a9ceb1de02ad008611539e93def346e78JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0518bb3f-2267-6695-0ffd-acd323606703&amp;u=a1aHR0cHM6Ly9zb2Npb2xvZ3kuaW5zdGl0dXRlL2ludHJvZHVjdGlvbi10by1zb2Npb2xvZ3kvdW5kZXJzdGFuZGluZy1jb21tdW5pdHktZGVmaW5pdGlvbnMtc29jaW9sb2dpc3RzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5b574e67f712d78e70378ed6933375d423ae9a050271ed45febcc2f30d3cea7fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWFyY2hpbmc&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4293d575e0015649c3fa11971a6bdebb457e8a85456d4adad96cc1744741d5fbJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1veTBxNlgyTnVSNA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=031bb03b312a817eddcd0b6d7b740979d0eaa26fbba94690db82625130a8a693JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly9lbi53aWtpcGVkaWEub3JnL3dpa2kvTWFyY2hpbmdfYmFuZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dce996492ddea473bcf38d4c729611729bcc426f8b3cd233ab5404151fdff570JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vTWFyY2g&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0fb6f12a9066f6d72cfef571c72bb5f27de4b8ca8866848365e8b4e8a0a6ec84JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vTWFyY2hpbmdEb3RDb20&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e95367a9e6238abcb1cf027d03cfa1209dc131b99763c645323509ceb7494314JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly93d3cuZmFjZWJvb2suY29tL01hcmNoaW5nRG90Q29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7304e485ee0e2d766fc750370e423bbf6d3dcb0ea885f0611134e3e4a11f6885JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly9kaWN0aW9uYXJ5LmNhbWJyaWRnZS5vcmcvZGljdGlvbmFyeS9lbmdsaXNoL21hcmNoaW5n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d9d188e4fa2e93770e1dd8073f14276c0b2934ccc4dcd446d062b6a86ff9cd1aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly9tYXJjaGluZy5jb20v&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ce94b491803052b8171de2c83726f33dbf74aad5293f2b8cc51f13562e173c70JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vTWFyY2gtSW4tTWFyY2hpbmctQmFuZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=45710bbebcc01726a30789e2dbd50d5a0c74ae270dccf4aea2f55983d9815721JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=17ce4705-78b7-6d7a-0367-50e979066cc0&amp;u=a1aHR0cHM6Ly93d3cuc2NyaWJkLmNvbS9kb2N1bWVudC83MTg1NTUwMi9NYXJjaGluZy1CYW5kLUZ1bmRhbWVudGFscw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=efc76d2ff6acf22e44322d4a1913c54f84cca933c52c816b2600f0ffcd52ea78JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL2JyYW1zZXMvY2hhdGdwdC1tZA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5446d0386a4e602a037d6d9e8d1942223a8c2bab360c8ecb0851b93c47231dabJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3RvcGljcy9jaGF0Z3B0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7fe2f9cd71dc3b7859887e593a631d4b6d2fbf2d0637d1d35eee77c86796b45fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3RvcGljLzI2NjkxODk1&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b2fc46854ae67fa6b582748d230b849437808ff53d179a19b2641879bed4bdbcJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0NoYXRHUFQvY29tbWVudHMvMTA3emZ4ay9yY2hhdGdwdHNfZmFxX3RocmVhZC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e972f7d4cc79cabaeaa133b041b579c01e386b1b96c23f9aa324b5d45fd66949JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly93d3cucmVkZGl0LmNvbS9yL0NoYXRHUFQvdG9wLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=213ec3d11b02a02bb02b4e8feaf3fa2f94a35acc943460a007ac495dcbed3af0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzU4NDQwMjMzMg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=561b87d8e5802f8f2c17bff9439b49f5ac76a07a8fc8da3534636aa3dc4f181eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL2JhZy14bWwvQ2hhdEdQVC1mb3ItTGVnYWN5LWlPUw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ccccb5a5a746b3a369f65920d52b218c59244c5dd5c181cf5d42f540feb0eee2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3RvcGljcy9jaGF0Z3B0LWFwaQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4fc0a922bb523ed9b4be0b7710b02f644fa8caf1f90d5de4ed99f521eb34ea1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL3RhaXNoaS1pL2F3ZXNvbWUtQ2hhdEdQVC1yZXBvc2l0b3JpZXM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8b1632640e40e9aea52c66fddbc48c4286a583abaebdcff219f194a1d52b92e9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=1cf72253-42bc-689b-3a20-35bf43a9693b&amp;u=a1aHR0cHM6Ly9naXRodWIuY29tL0xvbmdwYW5aaG91L0NoYXRHUFQtQnlwYXNz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8caaa0aac72c38f12319262a796b3af3c0a66e9bd001bf4d99659ef5c0ca83ecJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9leHBlcmllbmNlL2ZpbGVleHBsb3Jlci9maWxlLWV4cGxvcmVyLWluLXdpbmRvd3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=82a66b4168331d1903625729ace7961520256d79f18402fab8fbeaab7178965fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vR2V0LUhlbHAtd2l0aC1GaWxlLUV4cGxvcmVyLWluLVdpbmRvd3M&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=addbd8ee9bf1e0a3c74239b29f07b11396767b7a702290465ba699b5c8e5873aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly9nZWVremFnLmNvbS9ndWlkZXMvY29tcHV0ZXJzL2dldC1oZWxwLXdpdGgtZmlsZS1leHBsb3Jlci1pbi13aW5kb3dzLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=681951d653fc825afbb07d2cf06377c124cfddc56577d3b52db92bed96ae6916JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly93d3cubWljcm9zb2Z0LmNvbS9lbi11cy93aW5kb3dzL3RpcHMvZmlsZS1leHBsb3Jlcj9tc29ja2lkPTNlMzI4NzExM2VjZTZiNjQxNTliOTBmZDNmNTI2YTNj&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=4e3ee81147b229542ebe5ac5091d2ccf5eb5feed1abd52f3046f10665706634fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly93d3cud2lraWhvdy5jb20vT3Blbi1XaW5kb3dzLUV4cGxvcmVy&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6e45a2e99cccfca09df5628a048e81aab336566a87eebb4ecc362c89625470c0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly93d3cueW91dHViZS5jb20vd2F0Y2g_dj1uMG5hWXJpNkpYRQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=12bdfcc53aa52afd80c3479acf294d7422d06891d0dc738402aa3681c6055e98JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly93aW5kb3dzcmVwb3J0LmNvbS9nZXQtaGVscC13aXRoLWZpbGUtZXhwbG9yZXItaW4td2luZG93cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8ff825421c684a509c9a069b1a748af2d1f1221274702c9ee3c427f83f98a78cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly90ZWNoYmFrZWQuY29tL2dldC1oZWxwLWZpbGUtZXhwbG9yZXItd2luZG93cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=0573dc8c9be1c25a1462cc8ba656e4d6233823d1442460b093e5c567b4d1f9edJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly9nYWRnZXRzbnVydHVyZS5jb20vZ2V0LWhlbHAtd2l0aC1maWxlLWV4cGxvcmVyLWluLXdpbmRvd3MtMTEtb3ItMTAv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cb382a109e257a49a4e65c066cad71dd3516d93585b4083f906473d8eea03a51JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3e328711-3ece-6b64-159b-90fd3f526a3c&amp;u=a1aHR0cHM6Ly9vZmZpY2V0dXRvcmlhbC5uZXQvdHV0b3JpYWwvZ2V0LWhlbHAtd2l0aC1maWxlLWV4cGxvcmVyLWluLXdpbmRvd3MvMTM1NS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=73a196cc91c1effe7e3655751604c70d286ce826e0e60dc07a7f8639f98ea119JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=065a68df-728e-614e-28f8-7f3373eb60de&amp;u=a1aHR0cHM6Ly9pbi5ib29rbXlzaG93LmNvbS9leHBsb3JlL21vdmllcy1oeWRlcmFiYWQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b69aaf1dd9f36f78e4422cbf1f7e0d41d696b642d74f4d178e2c2cf77837f8b1JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=065a68df-728e-614e-28f8-7f3373eb60de&amp;u=a1aHR0cHM6Ly9pbi5ib29rbXlzaG93LmNvbS9oeWRlcmFiYWQvY2luZW1hcw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=344f2326a3b60401e7dbe6c5d260aa4c1c8b0908bb2bbcfcbdf6a3b4f0d596f2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=065a68df-728e-614e-28f8-7f3373eb60de&amp;u=a1aHR0cHM6Ly93d3cuZGlzdHJpY3QuaW4vbW92aWVzL0h5ZGVyYWJhZC1tb3ZpZS10aWNrZXRz&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1296a4bc8c1143a4f418add1a08bcc7f99d3b712f159f71fa4ad8b01a781585fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=065a68df-728e-614e-28f8-7f3373eb60de&amp;u=a1aHR0cHM6Ly90aWNrZXRuZXcuY29tL21vdmllcy9oeWRlcmFiYWQvY2luZW1hLWhhbGxzLWFuZC1tb3ZpZS10aGVhdHJl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3623db521d45e2e23ec20b136454110ac01e05fb8fbd4da632b4278a9e051860JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvMTA4MDE1NDM_aGw9ZW4&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98f2c98752c03e0e25355241cde2c1776db8ab69fb66c94d5ae02c8f845832eaJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZXR2Lz9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1742ccd8b97d2b0a7a931f3d9f547763ab70e1916052a69d2e9bb0752b8be63cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzE5MDMyMzE3NzU5ODA5MTMwNTE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2846408df2135184883d546c9cc1d6c43081ebc917707bc8733501f01e38dcd2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3RvcGljLzE5NTUwNTMyL2hvdA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=2361fdaad133533d9123c6f41d8dd355c1b22344c18b943f5f115cfd3420d44eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvNTc0MDc_aGw9emgtSGFudCZjbz1HRU5JRS5QbGF0Zm9ybSUzRERlc2t0b3A&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3c5df35d27db01e2dc900767acdbdd7a4d8b2b62ef1aee84512f634d125897a9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvMTY0Njg2MT9obD16aC1IYW5z&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd7bcc94cae7818c171704430f1d69d70e0ba48d2ecf3630367f7dc07151ea2aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS8_aGw9dGg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=7d5f8a80e6cac451e596a49b659592b0026f0fc97467b1fbce19e70e1c5bba05JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS8_aGw9dmk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd29770076e5d0df40aad5bba3a59b4ee842260b9f833a044569f5fca3f220b4JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvNjMwODI0ND9obD1lbg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=05b096a0ed03203e63e855762e6a516069c7167fb5a1974e6754dc4871db235aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=3c8955a3-7f70-67e5-2e3e-424f7ed16682&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lmdvb2dsZS5jb20veW91dHViZS9hbnN3ZXIvMTY1NTU2P2hsPW5s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bd2111de21e6ca2ed97714a964bdb45011eab4c1190d3ebb248e331c9ceb89f9JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26edb1b9-0988-6657-31e1-a65508b96773&amp;u=a1aHR0cHM6Ly9iYXJkLmdvb2dsZS5jb20vdS8xL2NoYXQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=ea5bd205cbb915707c1933dd30c9efad24b25d4657520610b081751cd6d6e726JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=26edb1b9-0988-6657-31e1-a65508b96773&amp;u=a1aHR0cHM6Ly9iYXJkLmdvb2dsZS5jb20vY2hhdC82OGJlYmIzODY4YzE5YjI3&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=9d60688fbfa516a7a6f85ecc1bba6790d62e225105ae61655164d3a43e9c3f83JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cuc2t5c2Nhbm5lci5jb20vcm91dGVzL3Npbi9rYnYvc2luZ2Fwb3JlLWNoYW5naS10by1rcmFiaS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f82bfda88a27c6475863502b3e9fcef33116d429b7ad58b1ce8081436c258f1aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cuc2t5c2Nhbm5lci5jby5pbi9yb3V0ZXMvc2luL2tidi9zaW5nYXBvcmUtY2hhbmdpLXRvLWtyYWJpLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=162791527dadf2d3fce640363616aecbaee4e9cf0d89bdcf377cfb9b37c3f68eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cuc2t5c2Nhbm5lci5jb20uc2cvcm91dGVzL3Npbi9rYnYvc2luZ2Fwb3JlLWNoYW5naS10by1rcmFiaS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=20bf7409e71e8ea081f0c1589e3fc40e808c9795384fb806ba92b5b12696fd7bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cubWFrZW15dHJpcC5jb20vaW50ZXJuYXRpb25hbC1mbGlnaHRzL3NpbmdhcG9yZS1rcmFiaS1jaGVhcC1haXJ0aWNrZXRzLmh0bWw_bXNvY2tpZD0zN2Y3OTZlYWQwZTI2MGYxMzExNDgxMDZkMTk5NjFlYg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=10c82929a073efa3b521d4532228593fd5258b131aad3a49bfe449b300de5279JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cuZmx5c2Nvb3QuY29tL2ZsaWdodHMvZW4vZmxpZ2h0cy1mcm9tLXNpbmdhcG9yZS10by1rcmFiaQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=1ac3e5f4298dd93409e178665ef60a080c55360711cbef12574e856d7b88cc61JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cuZXhwZWRpYS5jb20vbHAvZmxpZ2h0cy9zaW4va2J2L3NpbmdhcG9yZS10by1rcmFiaT9tc29ja2lkPTM3Zjc5NmVhZDBlMjYwZjEzMTE0ODEwNmQxOTk2MWVi&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=77e76ccfc42773c615867da8e0ae077ea60c3dbe94148612bbdfc5d023581198JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cuc2t5c2Nhbm5lci5jby5pbi9yb3V0ZXMvc2lucy9rYnYvc2luZ2Fwb3JlLXRvLWtyYWJpLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=29e8102fd7454ce888084e7cee315a5dffa564caf6e5bf1475596e7c0a1ba51cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cuc2t5c2Nhbm5lci5uZXQvcm91dGVzL3Npbi9rYnYvc2luZ2Fwb3JlLWNoYW5naS10by1rcmFiaS5odG1sP21zb2NraWQ9MzdmNzk2ZWFkMGUyNjBmMTMxMTQ4MTA2ZDE5OTYxZWI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7ac8082c03565f1422b75107e18b9c1118eac526f860baab7ce27c594da507aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cuc2t5c2Nhbm5lci5uZXQvZmxpZ2h0cy9mbGlnaHRzLWZyb20tY2l0eS10by1yZWdpb24vc2lucy80NDI5MjE0OC9jaGVhcC1mbGlnaHRzLWZyb20tc2luZ2Fwb3JlLXRvLWtyYWJpLXByb3ZpbmNlP21zb2NraWQ9MzdmNzk2ZWFkMGUyNjBmMTMxMTQ4MTA2ZDE5OTYxZWI&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dce7453c877def5ef8853ec627a3dae52d03bd1cdb7c4ba461f789a10e4efb65JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=37f796ea-d0e2-60f1-3114-8106d19961eb&amp;u=a1aHR0cHM6Ly93d3cuYm9va2luZy5jb20vZmxpZ2h0cy9yb3V0ZS9jaXR5LXRvLWNpdHkvc2ctc2luZ2Fwb3JlLXRvLXRoLWtyYWJpLmh0bWw_bXNvY2tpZD0zN2Y3OTZlYWQwZTI2MGYxMzExNDgxMDZkMTk5NjFlYg&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6df21e68953d8e17b25c97e0267a1adf1e6aa7d2cf8463d594a9830318c9eb62JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f1a134-7af2-69f5-2230-b6d87b1c6885&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzE0NDcxMzI3MzcwNDQyNjUwMjAuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=53f6df8364bf21b06b63e89fc06474b3e16c31f9af1d43994e6e3e754773b481JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f1a134-7af2-69f5-2230-b6d87b1c6885&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzMwMDQ4ODI5Mw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=42c7a91df8cb3edb932516b9fd9233d2f74ea0d1fc638a32dadbcfe4c8c8db4aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f1a134-7af2-69f5-2230-b6d87b1c6885&amp;u=a1aHR0cHM6Ly93d3cuemhpaHUuY29tL3F1ZXN0aW9uLzU0NzI2MTI0&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=dfaea723f58adf04a7c43b73e7b12917828a456d20906568d1ef28048968ab56JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f1a134-7af2-69f5-2230-b6d87b1c6885&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzU2NTY2NjUyLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=5c1958e6ada44cc24bd364f8e86640737b8897de4703d3036e13d7c22b2446fbJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f1a134-7af2-69f5-2230-b6d87b1c6885&amp;u=a1aHR0cHM6Ly93d3cuYW5zd2Vycy5jb20vdHJhdmVsLWluZm9ybWF0aW9uL1doYXRfaXNfdGhlX3NpemVfb2ZfUGhpbGlwcGluZV9wYXNzcG9ydF9waG90bw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=98b342b36ff493ea540625d44fadfe6f90d651e8cac2fb3a7f66baa082e91a17JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f1a134-7af2-69f5-2230-b6d87b1c6885&amp;u=a1aHR0cHM6Ly93d3cuYW5zd2Vycy5jb20vdHJhdmVsLWluZm9ybWF0aW9uL0hvd19kb195b3VfbWFrZV9wYXNzcG9ydF9zaXplX3Bob3RvX29uX3Bob3Rvc2hvcF9jczM&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=22fab7356627747b0b81863025d3dff7c94ff43c3c388d3c91d37758c3d2fb5eJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f1a134-7af2-69f5-2230-b6d87b1c6885&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzQ5NzE3OTE2NzY1MzYwODA0NC5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=e0d4db2e89a2dda3824a3b161af64d1585fa3cb0c444483a03d6300e994fb381JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f1a134-7af2-69f5-2230-b6d87b1c6885&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzY4NzU3OTgyLmh0bWw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a642117bb065dd23bbe845c14f3998eda0bc08d625174d9dadb7f833ab73bc0aJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=05f1a134-7af2-69f5-2230-b6d87b1c6885&amp;u=a1aHR0cHM6Ly96aGlkYW8uYmFpZHUuY29tL3F1ZXN0aW9uLzIyMDI2NDEyMzE0ODM3OTM4NjguaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6500ffa3667a64f49152d0d2f2376c2fab43486a253bf749ca13323b6315ab71JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cDovL21hZGh1cm1hdGthLmFwcC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b62ef68b1404c1cd54ecea31aca12e87e58a0f543c076138a6e630183c15bfc8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cHM6Ly9tYWRodXJzdGFybGluZS5jb20vbWFya2V0L3NhdHRhLW1hdGthLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a94d2fcf85fd816cacbf8b2bcd32165adb7ae8c01d27fd9b5d7b2e25f406e38bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cHM6Ly9zYXR0YW1hdGthMTEubmV0L2d1aWRlcy9tYXJrZXRzL3doYXQtaXMtbWFkaHVyLWRheS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=cc2a68d3e66e515a7e30ac6c3384e8a762ff8b01e2c2cd6019408f6d66b454ebJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cHM6Ly9zYXR0YW1hdGthb2ZmaWNlLmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8c80f1747e574ab3e4219921280924f096be809949b5ceb9b506207f0db8f3f0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cHM6Ly9zYXR0YW1hdGthdG9kYXkuY29tL2NoYXJ0L21hZGh1ci1tb3JuaW5n&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=68fc9809e733449faeed9091dc8f66c888f6d540152dd1c5f8d2097c8fb1458cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cHM6Ly9tYWRodXJsb3R0ZXJ5LmNvbS8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=565508e288017097d51964321a2d7f38080e339d0df85991188aa5a77e216707JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cHM6Ly9zaGl2cHVyc2F0dGFtYXRrYS5pbi9tYWRodXItbWF0a2EucGhw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b1d3bf884a7b103b581e024eaa27a029e5e3e0c5aaf2dc86e72ebf5517a9cb4fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cHM6Ly9zYXR0YW1hdGthdG9kYXkuY29tL2NoYXJ0L21hZGh1ci1kYXk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=edd45af10b5f7388a04e064039a294e49f4b65c5c287357b8b886b4dcdb005dbJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cHM6Ly9tYWRodXJtYXRrYXN1cGVyLmNvbS9tYWRodXItZGF5LXBhbmVsLWNoYXJ0LnBocA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=3eeb3a6d1de6e62c140b1d965c9c930757b4a97c0c51419414fa175b9ba4f798JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=21031c6b-133c-6b7c-144c-0b8712886a62&amp;u=a1aHR0cHM6Ly9zdXJham1hdGthLm9yZy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d706591ed824b32bb1d9632d5f69bc56450b24641bd11e2348c3566b9f4be43fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvd2luZG93cy9ob3ctdG8tZ2V0LWhlbHAtaW4td2luZG93cy03MTFiNjQ5Mi0wNDM1LTAwMzgtODcwNi03YzZiMGZlYjIwMGE&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=bf49159212b0c1ebbf82b13d0bc4232a342afe759635d9cea411b01a3c02b6e3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZW4tdXMvc3VwcG9ydC9nZXQtaGVscC9hYm91dC1nZXQtaGVscA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f009769c48c15617c4d52b98f6c14c598d0f849d79f6ac220313545bfa5661ffJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly93d3cuZWxldmVuZm9ydW0uY29tLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=96affce2cf23d517fa5b3ece5391bd4940c3ea10ce17c3d57ac1762b0417382cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly93d3cuZWxldmVuZm9ydW0uY29tL3QvZW5hYmxlLW9yLWRpc2FibGUtdGlwcy1hbmQtc3VnZ2VzdGlvbnMtbm90aWZpY2F0aW9ucy1pbi13aW5kb3dzLTExLjUyMDYv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6d5671ce3d7ff439b35f391e6eb3b88ae1f185bfc861fb9d2cf5e85c763091e2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vamEtanAvc3VwcG9ydC9nZXQtaGVscC9hYm91dC1nZXQtaGVscA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=566bce9406764bfafa67cbc6838c8663a3bd05b483c5ccf61f3c8e32cffc5078JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvc3VwcG9ydC9nZXQtaGVscC9hYm91dC1nZXQtaGVscA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=6df62f29097f4b6c703c6470916ad20a41b162d30eaf49d1c789f64dfddc034dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vcHQtYnIvd2luZG93cy9jb21vLW9idGVyLWFqdWRhLW5vLXdpbmRvd3MtNzExYjY0OTItMDQzNS0wMDM4LTg3MDYtN2M2YjBmZWIyMDBh&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=90a99a94bbfae84ab3748b3944352c208d988f3e868247adc9133d93f86293e3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZnItZnIvd2luZG93cy8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02a23a7d8f2493b7c337f12fbb028f13611591954f8c68ad12c03cada707f984JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vemgtdHcvc3VwcG9ydC9nZXQtaGVscC9hYm91dC1nZXQtaGVscA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=380def5a23b134308bd79dbefd5697b75a2472cf2b4ecd965906a5a75c022ed8JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=01970339-5601-69d8-1ac0-14d557d96863&amp;u=a1aHR0cHM6Ly9zdXBwb3J0Lm1pY3Jvc29mdC5jb20vZGUtZGUvc3VwcG9ydC9nZXQtaGVscC9ydW5uaW5nLXRyb3VibGVzaG9vdGVycy1pbi1nZXQtaGVscA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=446907bac7128b1a4ae786a282aae7792f1c1b34cba586fff86b71136a2b038cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20vZW4tVVMvZGVza3RvcC8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=c7fd7d30a779eaeab3b4bb83d7e56c4a9fc2031d7ca5167b51f7f85c27de82d2JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20vdGgtdGgvYmxvZy9wb3dlci1iaS1wcm8tcG93ZXItYmktcHJlbWl1bS1mbGV4aWJpbGl0eS10by1jaG9vc2UtdGhlLWxpY2Vuc2luZy1iZXN0LWZvci15b3UtYW5kLXlvdXItb3JnYW5pemF0aW9uLz9jZG49ZGlzYWJsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8fc9901f7fce1d63761647d43fd4302af0024e515dcaa68b57df349b52edf2deJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20vZGUtZGUvYmxvZy9uZXctZ2V0LWludHJvZHVjZWQtdG8tZGF4LXdpdGgtZ3VpZGVkLWxlYXJuaW5nLw&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=f6f3ae6299dd5a6ed18129a3c23885b020ba965f7d6c8b748da5411845de84e3JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20vcHQtcHQvYmxvZy9hbi1pbnRyb2R1Y3Rpb24tdG8tdGhlLXBvd2VyLWJpLWFkbWluLWNlbnRlci8&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=8d0aca376548daa772fe10c69d350d1ddbf211ba3f6b57c26f9805d7231a61e6JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20vZW4tZ2IvYmxvZy95b3VyLWRhdGEteW91ci12aXN1YWxpemF0aW9ucy15b3VyLXdheS13aXRoLXBvd2VyLWJpLz9jZG49ZGlzYWJsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=02bf177e90f500a6d90642d243b93b2e9aef1a5df00fb104dfddfcc7ff67a086JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20va28ta3IvYmxvZy9wdWJsaWMtcHJldmlldy1vZi1tdWx0aS1nZW8tZm9yLXBvd2VyLWJpLXByZW1pdW0vP2Nkbj1kaXNhYmxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=b67ce3fe9c0edb5b23f32117f8a7cd47c29b5569ef972720107be55bbad9816cJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20vZGUtZGUvYmxvZy91bmxvY2stcmV0YWlsLWludGVsbGlnZW5jZS13aXRoLXRoZS1wb3dlci1iaS1hcHAtYmFyY29kZS1zY2FubmVyLz9jZG49ZGlzYWJsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=a4d3eeb447821686be9d7a9ea5ce04fa979592dee7f03aa0e9ac50507c55e7cdJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20vcnUtcnUvYmxvZy9wb3dlci1iaS1tYXktMjAyMi1mZWF0dXJlLXN1bW1hcnkvP2Nkbj1kaXNhYmxl&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d52acbf3e584c2c757d5d956fe257b1c240fa50c6c4785cb60a5461b9b55fd6dJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20vaXQtaXQvYmxvZy92aXN1YWwtYXdlc29tZW5lc3MtdW5sb2NrZWQtdGhlLWZvcmNlLWRpcmVjdGVkLWdyYXBoLz9jZG49ZGlzYWJsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=58a43bf9da07bbe49dbb8da30a4ba3887c2c70679ff9d6b360d8e5739569accfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0fec439f-30aa-6dd5-1598-547331726cb1&amp;u=a1aHR0cHM6Ly9wb3dlcmJpLm1pY3Jvc29mdC5jb20vcHQtYnIvYmxvZy9hbmFseXppbmctYmxhY2stZnJpZGF5LWFuZC1jeWJlci1tb25kYXktcmVzdWx0cy13aXRoLXBvd2VyLWJpLz9jZG49ZGlzYWJsZQ&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=59ced5d85b3cd88cbabfd3327b5155af51d3f1c7d04f0e016a1d54e69c95cc3bJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0303940a-477e-63c5-3ea3-83e646ba62f2&amp;u=a1aHR0cHM6Ly93YWxscGFwZXJhY2Nlc3MuY29tL3NwaWRlci1tYW4tcmVk&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d01c486e08afd2b9eeb7e688339dc31918fd8750b9bff68b1650782515342fecJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0303940a-477e-63c5-3ea3-83e646ba62f2&amp;u=a1aHR0cHM6Ly93YWxscGFwZXJhY2Nlc3MuY29tL3JlZC1zcGlkZXItbWFu&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=89d35a928a67986dc13837a88d7914239b5525ca81a262718c18df12ef15b496JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0303940a-477e-63c5-3ea3-83e646ba62f2&amp;u=a1aHR0cHM6Ly80a3dhbGxwYXBlcnMuY29tL2dyYXBoaWNzLWNnaS9zcGlkZXItbWFuLW1hcnZlbC1zdXBlcmhlcm9lcy1yZWQtYmFja2dyb3VuZC1tYXJ2ZWwtY29taWNzLTc0OTQuaHRtbA&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=979d809cb2be7b2d4e362a3a4c9f5365422c41fd0bb16cf7cb3a1537725335b0JmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0303940a-477e-63c5-3ea3-83e646ba62f2&amp;u=a1aHR0cHM6Ly93YWxscGFwZXJzLmNvbS93YWxscGFwZXJzL3NwaWRlci1tYW4tcmVkLWJhY2tncm91bmQtNGstZDl4eXBrenFxcTRlZDRkaS5odG1s&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=af905dec06bfe8e31e51cea8595a8af942102f4d8e50eee578515ba71b72370fJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0303940a-477e-63c5-3ea3-83e646ba62f2&amp;u=a1aHR0cHM6Ly93YWxscGFwZXJzYWZhcmkuY29tL3JlZC1zcGlkZXItbWFuLXdhbGxwYXBlcnMv&amp;ntb=1</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/ck/a?!&amp;&amp;p=d7b6a44c46595c431805a83c1bdfa029b73661df92819603a71b8184429702cfJmltdHM9MTc5MTQxNzYwMA&amp;ptn=3&amp;ver=2&amp;hsh=4&amp;fclid=0303940a-477e-63c5-3ea3-83e646ba62f2&amp;u=a1aHR0cHM6Ly93d3cucGludGVyZXN0LmNvbS9pZGVhcy9yZWQtc3BpZGVyLW1hbi13YWxscGFwZXIvOTAxNTExNDExOTA0Lw&amp;ntb=1</t>
   </si>
   <si>
     <t>Cape Town CBD</t>
@@ -1399,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1433,19 +1559,19 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="G2" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H2" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1453,19 +1579,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="G3" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H3" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1473,19 +1599,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C4" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="G4" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H4" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1493,19 +1619,19 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="G5" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H5" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1513,19 +1639,19 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="G6" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H6" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1533,19 +1659,19 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="G7" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H7" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1553,19 +1679,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C8" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="G8" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H8" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1573,19 +1699,19 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="G9" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H9" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1593,19 +1719,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C10" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G10" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H10" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1613,19 +1739,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="G11" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H11" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1633,19 +1759,19 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="G12" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H12" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1653,19 +1779,19 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C13" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="G13" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H13" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1673,19 +1799,19 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="G14" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H14" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1693,19 +1819,19 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="G15" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H15" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1713,19 +1839,19 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="G16" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H16" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1733,19 +1859,19 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="G17" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H17" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1753,19 +1879,19 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="G18" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H18" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1773,19 +1899,19 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="G19" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H19" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1793,19 +1919,19 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C20" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="G20" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H20" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1813,19 +1939,19 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C21" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="G21" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H21" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1833,19 +1959,19 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C22" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="G22" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H22" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1853,19 +1979,19 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C23" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="G23" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H23" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1873,19 +1999,19 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C24" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="G24" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H24" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1893,19 +2019,19 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C25" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="G25" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H25" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1913,19 +2039,19 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C26" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="G26" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H26" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1933,19 +2059,19 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C27" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="G27" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H27" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1953,19 +2079,19 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C28" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="G28" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H28" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1973,19 +2099,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C29" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="G29" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H29" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1993,19 +2119,19 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="G30" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H30" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2013,19 +2139,19 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C31" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="G31" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H31" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2033,19 +2159,19 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="G32" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H32" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2053,19 +2179,19 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C33" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="G33" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H33" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -2073,19 +2199,19 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C34" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="G34" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H34" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2093,19 +2219,19 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C35" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="G35" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H35" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -2113,19 +2239,19 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="G36" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H36" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2133,19 +2259,19 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C37" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="G37" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H37" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -2153,19 +2279,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C38" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="G38" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H38" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2173,19 +2299,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C39" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="G39" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H39" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -2193,19 +2319,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C40" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="G40" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H40" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -2213,19 +2339,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C41" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="G41" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H41" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2233,19 +2359,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C42" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="G42" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H42" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2253,19 +2379,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C43" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="G43" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H43" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2273,19 +2399,19 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C44" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="G44" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H44" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2293,19 +2419,19 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C45" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="G45" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H45" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2313,19 +2439,19 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="G46" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H46" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -2333,19 +2459,19 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C47" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="G47" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H47" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2353,19 +2479,19 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C48" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="G48" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H48" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2373,19 +2499,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C49" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="G49" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H49" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2393,19 +2519,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C50" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="G50" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H50" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2413,19 +2539,19 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C51" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="G51" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H51" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2433,19 +2559,19 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C52" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="G52" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H52" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2453,19 +2579,19 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C53" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="G53" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H53" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2473,19 +2599,19 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C54" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="G54" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H54" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -2493,19 +2619,19 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C55" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G55" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H55" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2513,19 +2639,19 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C56" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="G56" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H56" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2533,19 +2659,19 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C57" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="G57" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H57" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2553,19 +2679,19 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="G58" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H58" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2573,19 +2699,19 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C59" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="G59" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H59" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2593,19 +2719,19 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C60" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="G60" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H60" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2613,19 +2739,19 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C61" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="G61" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H61" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2633,19 +2759,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C62" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="G62" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H62" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2653,19 +2779,19 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C63" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="G63" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H63" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2673,19 +2799,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C64" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="G64" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H64" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2693,19 +2819,19 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C65" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="G65" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H65" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2713,19 +2839,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C66" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="G66" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H66" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2733,19 +2859,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C67" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="G67" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H67" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2753,19 +2879,19 @@
         <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C68" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="G68" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H68" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2773,19 +2899,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C69" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="G69" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H69" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2793,19 +2919,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="G70" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H70" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2813,19 +2939,19 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C71" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="G71" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H71" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2833,19 +2959,19 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C72" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="G72" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H72" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2853,19 +2979,19 @@
         <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C73" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="G73" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H73" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2873,19 +2999,19 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C74" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="G74" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H74" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2893,19 +3019,19 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C75" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="G75" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H75" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2913,19 +3039,19 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C76" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="G76" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H76" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2933,19 +3059,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C77" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="G77" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H77" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2953,19 +3079,19 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C78" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G78" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H78" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2973,19 +3099,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C79" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="G79" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H79" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2993,19 +3119,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C80" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="G80" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H80" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3013,19 +3139,19 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C81" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="G81" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H81" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -3033,19 +3159,19 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C82" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="G82" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H82" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3053,19 +3179,19 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C83" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="G83" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H83" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3073,19 +3199,19 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C84" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="G84" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H84" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -3093,19 +3219,19 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C85" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="G85" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H85" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3113,19 +3239,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C86" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="G86" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H86" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -3133,19 +3259,19 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C87" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="G87" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H87" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3153,19 +3279,19 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C88" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="G88" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H88" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -3173,19 +3299,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C89" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="G89" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H89" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3193,19 +3319,19 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C90" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="G90" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H90" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3213,19 +3339,19 @@
         <v>97</v>
       </c>
       <c r="B91" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C91" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="G91" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H91" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -3233,19 +3359,19 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C92" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="G92" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H92" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3253,19 +3379,19 @@
         <v>99</v>
       </c>
       <c r="B93" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="G93" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="H93" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3273,19 +3399,19 @@
         <v>100</v>
       </c>
       <c r="B94" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C94" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="G94" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="H94" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3293,19 +3419,19 @@
         <v>101</v>
       </c>
       <c r="B95" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C95" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G95" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="H95" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3313,19 +3439,19 @@
         <v>102</v>
       </c>
       <c r="B96" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="G96" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="H96" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3333,19 +3459,19 @@
         <v>103</v>
       </c>
       <c r="B97" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C97" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="G97" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="H97" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3353,19 +3479,19 @@
         <v>104</v>
       </c>
       <c r="B98" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C98" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="G98" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="H98" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3373,19 +3499,19 @@
         <v>105</v>
       </c>
       <c r="B99" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C99" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="G99" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="H99" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3393,19 +3519,19 @@
         <v>106</v>
       </c>
       <c r="B100" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C100" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="G100" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="H100" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3413,19 +3539,19 @@
         <v>107</v>
       </c>
       <c r="B101" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C101" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="G101" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="H101" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3433,19 +3559,19 @@
         <v>108</v>
       </c>
       <c r="B102" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C102" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="G102" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="H102" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3453,19 +3579,19 @@
         <v>109</v>
       </c>
       <c r="B103" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C103" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="G103" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="H103" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3473,19 +3599,19 @@
         <v>110</v>
       </c>
       <c r="B104" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C104" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="G104" t="s">
-        <v>341</v>
+        <v>383</v>
       </c>
       <c r="H104" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3493,19 +3619,19 @@
         <v>111</v>
       </c>
       <c r="B105" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C105" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="G105" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H105" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -3513,19 +3639,19 @@
         <v>112</v>
       </c>
       <c r="B106" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C106" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="G106" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H106" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3533,19 +3659,19 @@
         <v>113</v>
       </c>
       <c r="B107" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C107" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="G107" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H107" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -3553,19 +3679,19 @@
         <v>114</v>
       </c>
       <c r="B108" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C108" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="G108" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H108" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3573,19 +3699,19 @@
         <v>115</v>
       </c>
       <c r="B109" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C109" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="G109" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H109" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -3593,19 +3719,19 @@
         <v>116</v>
       </c>
       <c r="B110" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C110" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="G110" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H110" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -3613,19 +3739,19 @@
         <v>117</v>
       </c>
       <c r="B111" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C111" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="G111" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H111" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3633,19 +3759,19 @@
         <v>118</v>
       </c>
       <c r="B112" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C112" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="G112" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H112" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3653,19 +3779,19 @@
         <v>119</v>
       </c>
       <c r="B113" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C113" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="G113" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H113" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -3673,19 +3799,19 @@
         <v>120</v>
       </c>
       <c r="B114" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C114" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="G114" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H114" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -3693,19 +3819,19 @@
         <v>121</v>
       </c>
       <c r="B115" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C115" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="G115" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H115" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -3713,19 +3839,19 @@
         <v>122</v>
       </c>
       <c r="B116" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C116" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="G116" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="H116" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -3733,19 +3859,19 @@
         <v>123</v>
       </c>
       <c r="B117" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C117" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="G117" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H117" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -3753,19 +3879,19 @@
         <v>124</v>
       </c>
       <c r="B118" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C118" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="G118" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H118" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3773,19 +3899,19 @@
         <v>125</v>
       </c>
       <c r="B119" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C119" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="G119" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H119" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3793,19 +3919,19 @@
         <v>126</v>
       </c>
       <c r="B120" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C120" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="G120" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H120" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3813,19 +3939,19 @@
         <v>127</v>
       </c>
       <c r="B121" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C121" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="G121" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H121" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3833,19 +3959,19 @@
         <v>128</v>
       </c>
       <c r="B122" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C122" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="G122" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H122" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -3853,19 +3979,19 @@
         <v>129</v>
       </c>
       <c r="B123" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C123" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="G123" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H123" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -3873,19 +3999,19 @@
         <v>130</v>
       </c>
       <c r="B124" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C124" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="G124" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H124" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -3893,19 +4019,19 @@
         <v>131</v>
       </c>
       <c r="B125" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C125" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="G125" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H125" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -3913,19 +4039,19 @@
         <v>132</v>
       </c>
       <c r="B126" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C126" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="G126" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H126" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -3933,19 +4059,19 @@
         <v>133</v>
       </c>
       <c r="B127" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C127" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="G127" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="H127" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3953,19 +4079,19 @@
         <v>134</v>
       </c>
       <c r="B128" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C128" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="G128" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="H128" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -3973,19 +4099,19 @@
         <v>135</v>
       </c>
       <c r="B129" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C129" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="G129" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="H129" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -3993,19 +4119,19 @@
         <v>136</v>
       </c>
       <c r="B130" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C130" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="G130" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="H130" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4013,19 +4139,19 @@
         <v>137</v>
       </c>
       <c r="B131" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C131" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="G131" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="H131" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4033,19 +4159,19 @@
         <v>138</v>
       </c>
       <c r="B132" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C132" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="G132" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="H132" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4053,19 +4179,19 @@
         <v>139</v>
       </c>
       <c r="B133" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C133" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="G133" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="H133" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4073,19 +4199,19 @@
         <v>140</v>
       </c>
       <c r="B134" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C134" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="G134" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="H134" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4093,19 +4219,19 @@
         <v>141</v>
       </c>
       <c r="B135" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C135" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="G135" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="H135" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4113,19 +4239,19 @@
         <v>142</v>
       </c>
       <c r="B136" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C136" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="G136" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="H136" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4133,19 +4259,19 @@
         <v>143</v>
       </c>
       <c r="B137" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C137" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="G137" t="s">
-        <v>343</v>
+        <v>385</v>
       </c>
       <c r="H137" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4153,19 +4279,19 @@
         <v>144</v>
       </c>
       <c r="B138" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C138" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="G138" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="H138" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -4173,19 +4299,19 @@
         <v>145</v>
       </c>
       <c r="B139" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C139" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="G139" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="H139" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -4193,19 +4319,19 @@
         <v>146</v>
       </c>
       <c r="B140" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C140" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="G140" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="H140" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4213,19 +4339,19 @@
         <v>147</v>
       </c>
       <c r="B141" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C141" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="G141" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="H141" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -4233,19 +4359,19 @@
         <v>148</v>
       </c>
       <c r="B142" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C142" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="G142" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="H142" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -4253,19 +4379,19 @@
         <v>149</v>
       </c>
       <c r="B143" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C143" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="G143" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="H143" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -4273,19 +4399,19 @@
         <v>150</v>
       </c>
       <c r="B144" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C144" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="G144" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="H144" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -4293,19 +4419,19 @@
         <v>151</v>
       </c>
       <c r="B145" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C145" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="G145" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="H145" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -4313,19 +4439,19 @@
         <v>152</v>
       </c>
       <c r="B146" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C146" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="G146" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="H146" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -4333,19 +4459,19 @@
         <v>153</v>
       </c>
       <c r="B147" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C147" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="G147" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="H147" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4353,19 +4479,19 @@
         <v>154</v>
       </c>
       <c r="B148" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C148" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="G148" t="s">
-        <v>344</v>
+        <v>386</v>
       </c>
       <c r="H148" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -4373,19 +4499,19 @@
         <v>155</v>
       </c>
       <c r="B149" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C149" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="G149" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H149" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -4393,19 +4519,19 @@
         <v>156</v>
       </c>
       <c r="B150" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C150" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="G150" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H150" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -4413,19 +4539,19 @@
         <v>157</v>
       </c>
       <c r="B151" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C151" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="G151" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H151" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -4433,19 +4559,19 @@
         <v>158</v>
       </c>
       <c r="B152" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C152" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="G152" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H152" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -4453,19 +4579,19 @@
         <v>159</v>
       </c>
       <c r="B153" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C153" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="G153" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H153" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4473,19 +4599,19 @@
         <v>160</v>
       </c>
       <c r="B154" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C154" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="G154" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H154" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -4493,19 +4619,19 @@
         <v>161</v>
       </c>
       <c r="B155" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C155" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="G155" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H155" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -4513,19 +4639,19 @@
         <v>162</v>
       </c>
       <c r="B156" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C156" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="G156" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H156" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -4533,19 +4659,19 @@
         <v>163</v>
       </c>
       <c r="B157" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C157" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="G157" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H157" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -4553,19 +4679,19 @@
         <v>164</v>
       </c>
       <c r="B158" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C158" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="G158" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H158" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -4573,19 +4699,19 @@
         <v>165</v>
       </c>
       <c r="B159" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C159" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="G159" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H159" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -4593,19 +4719,19 @@
         <v>166</v>
       </c>
       <c r="B160" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C160" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="G160" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H160" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -4613,19 +4739,19 @@
         <v>167</v>
       </c>
       <c r="B161" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C161" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="G161" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H161" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -4633,19 +4759,19 @@
         <v>168</v>
       </c>
       <c r="B162" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C162" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="G162" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H162" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -4653,19 +4779,19 @@
         <v>169</v>
       </c>
       <c r="B163" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C163" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="G163" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H163" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -4673,19 +4799,19 @@
         <v>170</v>
       </c>
       <c r="B164" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C164" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="G164" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H164" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -4693,19 +4819,19 @@
         <v>171</v>
       </c>
       <c r="B165" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C165" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="G165" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="H165" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -4713,19 +4839,439 @@
         <v>172</v>
       </c>
       <c r="B166" t="s">
+        <v>194</v>
+      </c>
+      <c r="C166" t="s">
+        <v>195</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G166" t="s">
+        <v>386</v>
+      </c>
+      <c r="H166" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" t="s">
         <v>173</v>
       </c>
-      <c r="C166" t="s">
+      <c r="B167" t="s">
+        <v>194</v>
+      </c>
+      <c r="C167" t="s">
+        <v>195</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G167" t="s">
+        <v>386</v>
+      </c>
+      <c r="H167" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" t="s">
         <v>174</v>
       </c>
-      <c r="F166" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="G166" t="s">
-        <v>345</v>
-      </c>
-      <c r="H166" t="s">
-        <v>346</v>
+      <c r="B168" t="s">
+        <v>194</v>
+      </c>
+      <c r="C168" t="s">
+        <v>195</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G168" t="s">
+        <v>386</v>
+      </c>
+      <c r="H168" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" t="s">
+        <v>175</v>
+      </c>
+      <c r="B169" t="s">
+        <v>194</v>
+      </c>
+      <c r="C169" t="s">
+        <v>195</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G169" t="s">
+        <v>386</v>
+      </c>
+      <c r="H169" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" t="s">
+        <v>176</v>
+      </c>
+      <c r="B170" t="s">
+        <v>194</v>
+      </c>
+      <c r="C170" t="s">
+        <v>195</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G170" t="s">
+        <v>386</v>
+      </c>
+      <c r="H170" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" t="s">
+        <v>177</v>
+      </c>
+      <c r="B171" t="s">
+        <v>194</v>
+      </c>
+      <c r="C171" t="s">
+        <v>195</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G171" t="s">
+        <v>386</v>
+      </c>
+      <c r="H171" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" t="s">
+        <v>178</v>
+      </c>
+      <c r="B172" t="s">
+        <v>194</v>
+      </c>
+      <c r="C172" t="s">
+        <v>195</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G172" t="s">
+        <v>387</v>
+      </c>
+      <c r="H172" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" t="s">
+        <v>179</v>
+      </c>
+      <c r="B173" t="s">
+        <v>194</v>
+      </c>
+      <c r="C173" t="s">
+        <v>195</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G173" t="s">
+        <v>387</v>
+      </c>
+      <c r="H173" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" t="s">
+        <v>180</v>
+      </c>
+      <c r="B174" t="s">
+        <v>194</v>
+      </c>
+      <c r="C174" t="s">
+        <v>195</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G174" t="s">
+        <v>387</v>
+      </c>
+      <c r="H174" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" t="s">
+        <v>181</v>
+      </c>
+      <c r="B175" t="s">
+        <v>194</v>
+      </c>
+      <c r="C175" t="s">
+        <v>195</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G175" t="s">
+        <v>387</v>
+      </c>
+      <c r="H175" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" t="s">
+        <v>182</v>
+      </c>
+      <c r="B176" t="s">
+        <v>194</v>
+      </c>
+      <c r="C176" t="s">
+        <v>195</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G176" t="s">
+        <v>387</v>
+      </c>
+      <c r="H176" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" t="s">
+        <v>183</v>
+      </c>
+      <c r="B177" t="s">
+        <v>194</v>
+      </c>
+      <c r="C177" t="s">
+        <v>195</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G177" t="s">
+        <v>387</v>
+      </c>
+      <c r="H177" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" t="s">
+        <v>184</v>
+      </c>
+      <c r="B178" t="s">
+        <v>194</v>
+      </c>
+      <c r="C178" t="s">
+        <v>195</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="G178" t="s">
+        <v>387</v>
+      </c>
+      <c r="H178" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" t="s">
+        <v>185</v>
+      </c>
+      <c r="B179" t="s">
+        <v>194</v>
+      </c>
+      <c r="C179" t="s">
+        <v>195</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G179" t="s">
+        <v>387</v>
+      </c>
+      <c r="H179" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" t="s">
+        <v>186</v>
+      </c>
+      <c r="B180" t="s">
+        <v>194</v>
+      </c>
+      <c r="C180" t="s">
+        <v>195</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G180" t="s">
+        <v>387</v>
+      </c>
+      <c r="H180" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" t="s">
+        <v>187</v>
+      </c>
+      <c r="B181" t="s">
+        <v>194</v>
+      </c>
+      <c r="C181" t="s">
+        <v>195</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G181" t="s">
+        <v>387</v>
+      </c>
+      <c r="H181" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" t="s">
+        <v>188</v>
+      </c>
+      <c r="B182" t="s">
+        <v>194</v>
+      </c>
+      <c r="C182" t="s">
+        <v>195</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G182" t="s">
+        <v>387</v>
+      </c>
+      <c r="H182" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" t="s">
+        <v>189</v>
+      </c>
+      <c r="B183" t="s">
+        <v>194</v>
+      </c>
+      <c r="C183" t="s">
+        <v>195</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G183" t="s">
+        <v>387</v>
+      </c>
+      <c r="H183" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" t="s">
+        <v>190</v>
+      </c>
+      <c r="B184" t="s">
+        <v>194</v>
+      </c>
+      <c r="C184" t="s">
+        <v>195</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="G184" t="s">
+        <v>387</v>
+      </c>
+      <c r="H184" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" t="s">
+        <v>191</v>
+      </c>
+      <c r="B185" t="s">
+        <v>194</v>
+      </c>
+      <c r="C185" t="s">
+        <v>195</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="G185" t="s">
+        <v>387</v>
+      </c>
+      <c r="H185" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" t="s">
+        <v>192</v>
+      </c>
+      <c r="B186" t="s">
+        <v>194</v>
+      </c>
+      <c r="C186" t="s">
+        <v>195</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G186" t="s">
+        <v>387</v>
+      </c>
+      <c r="H186" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" t="s">
+        <v>193</v>
+      </c>
+      <c r="B187" t="s">
+        <v>194</v>
+      </c>
+      <c r="C187" t="s">
+        <v>195</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G187" t="s">
+        <v>387</v>
+      </c>
+      <c r="H187" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4895,6 +5441,27 @@
     <hyperlink ref="F164" r:id="rId163"/>
     <hyperlink ref="F165" r:id="rId164"/>
     <hyperlink ref="F166" r:id="rId165"/>
+    <hyperlink ref="F167" r:id="rId166"/>
+    <hyperlink ref="F168" r:id="rId167"/>
+    <hyperlink ref="F169" r:id="rId168"/>
+    <hyperlink ref="F170" r:id="rId169"/>
+    <hyperlink ref="F171" r:id="rId170"/>
+    <hyperlink ref="F172" r:id="rId171"/>
+    <hyperlink ref="F173" r:id="rId172"/>
+    <hyperlink ref="F174" r:id="rId173"/>
+    <hyperlink ref="F175" r:id="rId174"/>
+    <hyperlink ref="F176" r:id="rId175"/>
+    <hyperlink ref="F177" r:id="rId176"/>
+    <hyperlink ref="F178" r:id="rId177"/>
+    <hyperlink ref="F179" r:id="rId178"/>
+    <hyperlink ref="F180" r:id="rId179"/>
+    <hyperlink ref="F181" r:id="rId180"/>
+    <hyperlink ref="F182" r:id="rId181"/>
+    <hyperlink ref="F183" r:id="rId182"/>
+    <hyperlink ref="F184" r:id="rId183"/>
+    <hyperlink ref="F185" r:id="rId184"/>
+    <hyperlink ref="F186" r:id="rId185"/>
+    <hyperlink ref="F187" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
